--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -6759,8 +6759,14 @@
       <c r="A287" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>561</v>
+      <c r="B287" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Power = 5 kW. Theoretical capacity = 40 kWh. Energy density = 15 Wh/kg. Discharge voltage per cell = 1.25 V. Number of cells = 11. Weight = 2616 kg. Electrolyte replacement frequency = 22 times. Number of cycles the flow battery can perform before electrolyte replacement = 371 cycles. Total energy delivery = 196 MWh. Technology readines level of the HFB: TRL=∼4. 
+End-of-life (EoL) was not considered because of high uncertainty related to the recycling technology for TEMPO-based electrolyte used in the OFB and HFB.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
@@ -6940,8 +6946,14 @@
       <c r="A301" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>562</v>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Power = 5 kW. Theoretical capacity = 40 kWh. Energy density = 16 Wh/kg. Discharge voltage per cell = 1 V. Number of cells = 13. Weight = 2470 kg. Electrolyte replacement frequency = 9 times. Number of cycles the flow battery can perform before electrolyte replacement = 851 cycles. Total energy delivery = 185 MWh. Technology readines level of the HFB: TRL=∼4. 
+End-of-life (EoL) was not considered because of high uncertainty related to the recycling technology for TEMPO-based electrolyte used in the OFB and HFB.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
@@ -7317,8 +7329,12 @@
       <c r="A330" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>472</v>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
@@ -7450,27 +7466,13 @@
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A338" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B338" s="1">
-        <v>124</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="G338" s="1" t="s">
-        <v>510</v>
-      </c>
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
@@ -7585,8 +7587,12 @@
       <c r="A348" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>472</v>
+      <c r="B348" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
@@ -7672,27 +7678,13 @@
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A354" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B354" s="1">
-        <v>124</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="G354" s="1" t="s">
-        <v>510</v>
-      </c>
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+      <c r="E354" s="1"/>
+      <c r="F354" s="1"/>
+      <c r="G354" s="1"/>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
@@ -15461,8 +15453,15 @@
       <c r="A787" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B787" s="1" t="s">
-        <v>547</v>
+      <c r="B787" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The RFBs comprise three main parts: a power subsystem (cell stack), an energy subsystem including electrolytes and container tanks, and a periphery with ancillary components. The RFBs were designed with a power rating of 5 kW and a theoretical capacity of 40 kWh.
+End-of-life (EoL) was not considered because of the high uncertainty related to the recycling technology for TEMPO-based electrolyte used in the OFB and the HFB.
+TRL =  4 aprox.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.2">
@@ -15614,8 +15613,15 @@
       <c r="A800" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B800" s="1" t="s">
-        <v>547</v>
+      <c r="B800" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The RFBs comprise three main parts: a power subsystem (cell stack), an energy subsystem including electrolytes and container tanks, and a periphery with ancillary components. The RFBs were designed with a power rating of 5 kW and a theoretical capacity of 40 kWh.
+End-of-life (EoL) was not considered because of the high uncertainty related to the recycling technology for TEMPO-based electrolyte used in the OFB and the HFB.
+TRL =  4 aprox.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="801" spans="1:10" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N933"/>
+  <dimension ref="A1:N963"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -7800,8 +7800,14 @@
       <c r="A364" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>526</v>
+      <c r="B364" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TEMPTMA was modeled based on the production process described by "Worldwide Pat., 2016". First, TAA is reacted with dimethylamine under palladium-C catalyst at -10°C. Hydrogen is then added to the reaction mixture at 60°C. Afterwards, the catalyst is filtered and reused in the same process. The solvent was recirculated as well. In this step, Intermediate 1 is produced. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛. 
+Intermediate 1 obtained in the previous step is dissolved in a 1:1 mixture of acetonitrile and toluene and transferred to a pressure reactor. After that, the reaction mixture is heated to 70°C, and chloromethane is added. Then, the precipitation is collected by reducing the temperature to 20°C. The precipitation is then washed with toluene, to obtain Intermediate 2. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛. 
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
@@ -8137,6 +8143,36 @@
       </c>
       <c r="H380" s="1" t="s">
         <v>261</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+      <c r="B381">
+        <v>1</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
@@ -18004,6 +18040,558 @@
         <v>572</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B946">
+        <v>0.10526315789473685</v>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>market for activated carbon, granular</t>
+        </is>
+      </c>
+      <c r="B947">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>activated carbon, granular</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>activated carbon, granular</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B948">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B949">
+        <v>1</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B954">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+      <c r="B961">
+        <v>1</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B962">
+        <v>0.0024878048780487805</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B963">
+        <v>-0.0024878048780487805</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N963"/>
+  <dimension ref="A1:N979"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -13737,8 +13737,13 @@
       <c r="A687" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B687" s="1" t="s">
-        <v>537</v>
+      <c r="B687" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BULK Al END-PLATE SUPPLY, issue81,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Source design uses aluminium endplates; workbook specifies10mm thickness but buys batterycurrentcollectorfoil. Replace that supplier at the same1kg finishedplate/kg endplate with a scopedbulkplate reference: genericwroughtAl supply,aluminium sheet/plate rolling service and averageAl product finishing service. No additional lithium-ion battery,highpuritycollector architecture orAlLi alloy is required. Preserve installedHFB49.49331859090909kg andOFB26.731447961538468kg endplates, existingarea/count and nominal40kWh design. Actual plate alloy is unspecified; use the genericwroughtalloy supplymix as a declared forming-compatible proxy, not a certified6061plate or pureprimaryAl claim.95% totalmetalretention is an explicitengineeringassumption,test90-100%; buy1/0.95kgAl and matchinggrossrolling service,finish1kg netplate,dispose1/0.95-1kg mixed manufacturingoffcut. Native metalworking services exclude the separately requiredmetal feed; do not treat servicekg as anotherkg retainedAl. Generic hazardous-incineration is a manufacturingloss-fate proxy,not an endorsed commercialAlscrap route or an addedrecoverycredit. Actual net/gross dimensions,drilledholes,bolting tolerance,alloyingcomposition,processingyield and futureweight reduction need engineeringverification. This change replaces a foilmanufacturing proxy; it does not assert the finishedplate masses are optimized or sourcefullyreproduced. No separatefullsystemreplacement or duplicatedplate purchase. Preserve source exclusionofbatteryEOL and all other subsystemrecipes; no native,runtime,YAML or primary-secondaryshare edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+the thickness of the end plate is 10 mm, which is similar to that of Al foill. 
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.2">
@@ -13833,14 +13838,18 @@
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A696" s="1" t="s">
-        <v>80</v>
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
       </c>
       <c r="B696" s="1">
         <v>1</v>
       </c>
-      <c r="C696" s="1" t="s">
-        <v>38</v>
+      <c r="C696" s="1" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D696" s="1" t="s">
         <v>19</v>
@@ -13851,8 +13860,10 @@
       <c r="F696" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="G696" s="1" t="s">
-        <v>290</v>
+      <c r="G696" s="1" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.2">
@@ -18592,6 +18603,317 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B968">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BULK Al END-PLATE SUPPLY, issue81,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Source design uses aluminium endplates; workbook specifies10mm thickness but buys batterycurrentcollectorfoil. Replace that supplier at the same1kg finishedplate/kg endplate with a scopedbulkplate reference: genericwroughtAl supply,aluminium sheet/plate rolling service and averageAl product finishing service. No additional lithium-ion battery,highpuritycollector architecture orAlLi alloy is required. Preserve installedHFB49.49331859090909kg andOFB26.731447961538468kg endplates, existingarea/count and nominal40kWh design. Actual plate alloy is unspecified; use the genericwroughtalloy supplymix as a declared forming-compatible proxy, not a certified6061plate or pureprimaryAl claim.95% totalmetalretention is an explicitengineeringassumption,test90-100%; buy1/0.95kgAl and matchinggrossrolling service,finish1kg netplate,dispose1/0.95-1kg mixed manufacturingoffcut. Native metalworking services exclude the separately requiredmetal feed; do not treat servicekg as anotherkg retainedAl. Generic hazardous-incineration is a manufacturingloss-fate proxy,not an endorsed commercialAlscrap route or an addedrecoverycredit. Actual net/gross dimensions,drilledholes,bolting tolerance,alloyingcomposition,processingyield and futureweight reduction need engineeringverification. This change replaces a foilmanufacturing proxy; it does not assert the finishedplate masses are optimized or sourcefullyreproduced. No separatefullsystemreplacement or duplicatedplate purchase. Preserve source exclusionofbatteryEOL and all other subsystemrecipes; no native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
+      </c>
+      <c r="B975">
+        <v>1</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B976">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B977">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B978">
+        <v>1</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B979">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N979"/>
+  <dimension ref="A1:N995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -5802,8 +5802,13 @@
       <c r="A219" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>524</v>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED ZINC-FOIL PROCESS IDENTITY, issue82,2026-10-18. Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition. Replace the active HFB zincfelt proxy,which boughtAlcastingfacility andCusheetrolling,by a distinct1kg netpure-Zn foil reference. Retain HFBinstalledZn electrode4.94kg and all existing stackcellarea/count; do not infer porousfelt volume,density or morphology. Retained metal is1kgZn,not addedCu/Al merelybecause former processproxies namedthosemetals. Use existingrefinedZn marketat1/0.95kg,explicit95% totalcasting/rollingretention,test90-100%,matched1/0.95-1kg manufacturingresidue. Use an electricinduction melting/casting+rolling engineeringroute: zincspecificheat0.388kJ/kgK,latentheat112kJ/kg,reference20-25Cfeedheatedto500C,idealheat0.2963MJ/kg;50% melterefficiency and0.05kWh/kg rollingallowance give0.22590643274853806kWh/kg netfoil. These thermalconstants andselectedefficiency/rollingelectricity are engineeringreferences,not a measured electrodefoilline. Testmelterefficiency30-80%,rolling0.01-0.1kWh/kg andyield90-100%. Do not read EPD cumulativeA1-A3 environmentalenergyindicators as processfuel consumption,which would doublecountrefinedZnproduction. Transfer only its documentedprocessarchitecture and0.08g/kg lubricant coefficient; do not transferbuildingalloyCu/Ti additions,coating,longbuildinglife or moduleDcredits. Genericlubricatingoil is the emulsion-supplyproxy;coolingwater,emulsiondilution,highpuritypowder/foilprocessing,surfacepreparation andfactoryequipmentareunresolved. Manufacturingwaste usesmixedhazardoustreatment proxy without inventedZnrecoverycredit. Legacyfeltprovider remainsavailable but theHFB stackbuys only the newfoilreference at unchangedmass. Metalcharacterization mustfollowrealZn feed,not a copper-shapingservice. No native,runtime,YAML edits or primary-secondaryshare changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The RFBs comprise three main parts: a power subsystem (cell stack), an energy subsystem including electrolytes and container tanks, and a periphery with ancillary components. The RFBs were designed with a power rating of 5 kW and a theoretical capacity of 40 kWh.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -6050,14 +6055,18 @@
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A232" s="1" t="s">
-        <v>536</v>
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
       </c>
       <c r="B232" s="1">
         <v>4.9399999999999995</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>38</v>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D232" s="1" t="s">
         <v>19</v>
@@ -6068,8 +6077,10 @@
       <c r="F232" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G232" s="1" t="s">
-        <v>76</v>
+      <c r="G232" s="1" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -13593,8 +13604,12 @@
       <c r="A677" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B677" s="1" t="s">
-        <v>472</v>
+      <c r="B677" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED ZINC-FOIL PROCESS IDENTITY, issue82,2026-10-18. Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition. Replace the active HFB zincfelt proxy,which boughtAlcastingfacility andCusheetrolling,by a distinct1kg netpure-Zn foil reference. Retain HFBinstalledZn electrode4.94kg and all existing stackcellarea/count; do not infer porousfelt volume,density or morphology. Retained metal is1kgZn,not addedCu/Al merelybecause former processproxies namedthosemetals. Use existingrefinedZn marketat1/0.95kg,explicit95% totalcasting/rollingretention,test90-100%,matched1/0.95-1kg manufacturingresidue. Use an electricinduction melting/casting+rolling engineeringroute: zincspecificheat0.388kJ/kgK,latentheat112kJ/kg,reference20-25Cfeedheatedto500C,idealheat0.2963MJ/kg;50% melterefficiency and0.05kWh/kg rollingallowance give0.22590643274853806kWh/kg netfoil. These thermalconstants andselectedefficiency/rollingelectricity are engineeringreferences,not a measured electrodefoilline. Testmelterefficiency30-80%,rolling0.01-0.1kWh/kg andyield90-100%. Do not read EPD cumulativeA1-A3 environmentalenergyindicators as processfuel consumption,which would doublecountrefinedZnproduction. Transfer only its documentedprocessarchitecture and0.08g/kg lubricant coefficient; do not transferbuildingalloyCu/Ti additions,coating,longbuildinglife or moduleDcredits. Genericlubricatingoil is the emulsion-supplyproxy;coolingwater,emulsiondilution,highpuritypowder/foilprocessing,surfacepreparation andfactoryequipmentareunresolved. Manufacturingwaste usesmixedhazardoustreatment proxy without inventedZnrecoverycredit. Legacyfeltprovider remainsavailable but theHFB stackbuys only the newfoilreference at unchangedmass. Metalcharacterization mustfollowrealZn feed,not a copper-shapingservice. No native,runtime,YAML edits or primary-secondaryshare changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.2">
@@ -18914,6 +18929,317 @@
         </is>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B984">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>APPROVED ZINC-FOIL PROCESS IDENTITY, issue82,2026-10-18. Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition. Replace the active HFB zincfelt proxy,which boughtAlcastingfacility andCusheetrolling,by a distinct1kg netpure-Zn foil reference. Retain HFBinstalledZn electrode4.94kg and all existing stackcellarea/count; do not infer porousfelt volume,density or morphology. Retained metal is1kgZn,not addedCu/Al merelybecause former processproxies namedthosemetals. Use existingrefinedZn marketat1/0.95kg,explicit95% totalcasting/rollingretention,test90-100%,matched1/0.95-1kg manufacturingresidue. Use an electricinduction melting/casting+rolling engineeringroute: zincspecificheat0.388kJ/kgK,latentheat112kJ/kg,reference20-25Cfeedheatedto500C,idealheat0.2963MJ/kg;50% melterefficiency and0.05kWh/kg rollingallowance give0.22590643274853806kWh/kg netfoil. These thermalconstants andselectedefficiency/rollingelectricity are engineeringreferences,not a measured electrodefoilline. Testmelterefficiency30-80%,rolling0.01-0.1kWh/kg andyield90-100%. Do not read EPD cumulativeA1-A3 environmentalenergyindicators as processfuel consumption,which would doublecountrefinedZnproduction. Transfer only its documentedprocessarchitecture and0.08g/kg lubricant coefficient; do not transferbuildingalloyCu/Ti additions,coating,longbuildinglife or moduleDcredits. Genericlubricatingoil is the emulsion-supplyproxy;coolingwater,emulsiondilution,highpuritypowder/foilprocessing,surfacepreparation andfactoryequipmentareunresolved. Manufacturingwaste usesmixedhazardoustreatment proxy without inventedZnrecoverycredit. Legacyfeltprovider remainsavailable but theHFB stackbuys only the newfoilreference at unchangedmass. Metalcharacterization mustfollowrealZn feed,not a copper-shapingservice. No native,runtime,YAML edits or primary-secondaryshare changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
+      </c>
+      <c r="B991">
+        <v>1</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>zinc foil electrode, casting and rolling engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B992">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B993">
+        <v>0.22590643274853806</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>market for lubricating oil</t>
+        </is>
+      </c>
+      <c r="B994">
+        <v>8.421052631578949e-05</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B995">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N995"/>
+  <dimension ref="A1:N1192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -14103,8 +14103,14 @@
       <c r="A716" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B716" s="1" t="s">
-        <v>544</v>
+      <c r="B716" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+total weight: 18 kg.              Data is from report: Life cycle assessment of low power solar inverters (2.5 to 20 kW) authors: Laura Tschümperlin, Philippe Stolz, Rolf Frischknecht. Data directly collected from producer.  
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.2">
@@ -14185,46 +14191,57 @@
       <c r="H724" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A725" s="1" t="s">
-        <v>14</v>
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
       </c>
       <c r="B725" s="1">
-        <v>60.9</v>
-      </c>
-      <c r="D725" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E725" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F725" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G725" s="1" t="s">
-        <v>252</v>
+        <v>1</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D725" s="1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E725" s="1"/>
+      <c r="F725" s="1" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G725" s="1"/>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits.</t>
+        </is>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A726" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B726" s="1">
-        <v>6.0600000000000001E-2</v>
-      </c>
-      <c r="D726" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E726" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F726" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G726" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="A726" s="1"/>
+      <c r="B726" s="1"/>
+      <c r="D726" s="1"/>
+      <c r="E726" s="1"/>
+      <c r="F726" s="1"/>
+      <c r="G726" s="1"/>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A727" s="1" t="s">
@@ -14250,1223 +14267,481 @@
       </c>
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A728" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B728" s="1">
-        <v>0.33900000000000002</v>
-      </c>
-      <c r="C728" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D728" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F728" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G728" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H728" s="1" t="s">
-        <v>406</v>
-      </c>
+      <c r="A728" s="1"/>
+      <c r="B728" s="1"/>
+      <c r="C728" s="1"/>
+      <c r="D728" s="1"/>
+      <c r="F728" s="1"/>
+      <c r="G728" s="8"/>
+      <c r="H728" s="1"/>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A729" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B729" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C729" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D729" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F729" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G729" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H729" s="1" t="s">
-        <v>407</v>
-      </c>
+      <c r="A729" s="1"/>
+      <c r="B729" s="1"/>
+      <c r="C729" s="1"/>
+      <c r="D729" s="1"/>
+      <c r="F729" s="1"/>
+      <c r="G729" s="8"/>
+      <c r="H729" s="1"/>
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A730" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B730" s="1">
-        <v>3.8400000000000001E-4</v>
-      </c>
-      <c r="C730" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D730" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F730" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G730" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H730" s="1" t="s">
-        <v>408</v>
-      </c>
+      <c r="A730" s="1"/>
+      <c r="B730" s="1"/>
+      <c r="C730" s="1"/>
+      <c r="D730" s="1"/>
+      <c r="F730" s="1"/>
+      <c r="G730" s="8"/>
+      <c r="H730" s="1"/>
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A731" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B731" s="1">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="C731" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D731" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F731" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G731" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H731" s="1" t="s">
-        <v>409</v>
-      </c>
+      <c r="A731" s="1"/>
+      <c r="B731" s="1"/>
+      <c r="C731" s="1"/>
+      <c r="D731" s="1"/>
+      <c r="F731" s="1"/>
+      <c r="G731" s="8"/>
+      <c r="H731" s="1"/>
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A732" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B732" s="1">
-        <v>3.2200000000000002E-3</v>
-      </c>
-      <c r="C732" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D732" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F732" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G732" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H732" s="1" t="s">
-        <v>410</v>
-      </c>
+      <c r="A732" s="1"/>
+      <c r="B732" s="1"/>
+      <c r="C732" s="1"/>
+      <c r="D732" s="1"/>
+      <c r="F732" s="1"/>
+      <c r="G732" s="8"/>
+      <c r="H732" s="1"/>
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A733" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B733" s="1">
-        <v>3.9100000000000003E-2</v>
-      </c>
-      <c r="C733" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D733" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F733" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G733" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H733" s="1" t="s">
-        <v>411</v>
-      </c>
+      <c r="A733" s="1"/>
+      <c r="B733" s="1"/>
+      <c r="C733" s="1"/>
+      <c r="D733" s="1"/>
+      <c r="F733" s="1"/>
+      <c r="G733" s="8"/>
+      <c r="H733" s="1"/>
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A734" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B734" s="1">
-        <v>5.5899999999999998E-2</v>
-      </c>
-      <c r="C734" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D734" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F734" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G734" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H734" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="A734" s="1"/>
+      <c r="B734" s="1"/>
+      <c r="C734" s="1"/>
+      <c r="D734" s="1"/>
+      <c r="F734" s="1"/>
+      <c r="G734" s="8"/>
+      <c r="H734" s="1"/>
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A735" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B735" s="1">
-        <v>4.0899999999999998E-5</v>
-      </c>
-      <c r="C735" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D735" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F735" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G735" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H735" s="1" t="s">
-        <v>412</v>
-      </c>
+      <c r="A735" s="1"/>
+      <c r="B735" s="1"/>
+      <c r="C735" s="1"/>
+      <c r="D735" s="1"/>
+      <c r="F735" s="1"/>
+      <c r="G735" s="8"/>
+      <c r="H735" s="1"/>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A736" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B736" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="C736" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D736" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F736" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G736" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H736" s="1" t="s">
-        <v>413</v>
-      </c>
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="1"/>
+      <c r="D736" s="1"/>
+      <c r="F736" s="1"/>
+      <c r="G736" s="8"/>
+      <c r="H736" s="1"/>
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A737" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B737" s="1">
-        <v>0.20899999999999999</v>
-      </c>
-      <c r="C737" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D737" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F737" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G737" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H737" s="1" t="s">
-        <v>414</v>
-      </c>
+      <c r="A737" s="1"/>
+      <c r="B737" s="1"/>
+      <c r="C737" s="1"/>
+      <c r="D737" s="1"/>
+      <c r="F737" s="1"/>
+      <c r="G737" s="8"/>
+      <c r="H737" s="1"/>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A738" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B738" s="1">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="C738" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D738" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F738" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G738" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H738" s="1" t="s">
-        <v>414</v>
-      </c>
+      <c r="A738" s="1"/>
+      <c r="B738" s="1"/>
+      <c r="C738" s="1"/>
+      <c r="D738" s="1"/>
+      <c r="F738" s="1"/>
+      <c r="G738" s="8"/>
+      <c r="H738" s="1"/>
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A739" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B739" s="1">
-        <v>0.36099999999999999</v>
-      </c>
-      <c r="C739" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D739" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F739" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G739" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H739" s="1" t="s">
-        <v>349</v>
-      </c>
+      <c r="A739" s="1"/>
+      <c r="B739" s="1"/>
+      <c r="C739" s="1"/>
+      <c r="D739" s="1"/>
+      <c r="F739" s="1"/>
+      <c r="G739" s="8"/>
+      <c r="H739" s="1"/>
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A740" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B740" s="1">
-        <v>5.72</v>
-      </c>
-      <c r="C740" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D740" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F740" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G740" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H740" s="1" t="s">
-        <v>278</v>
-      </c>
+      <c r="A740" s="1"/>
+      <c r="B740" s="1"/>
+      <c r="C740" s="1"/>
+      <c r="D740" s="1"/>
+      <c r="F740" s="1"/>
+      <c r="G740" s="8"/>
+      <c r="H740" s="1"/>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A741" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B741" s="1">
-        <v>1.7700000000000001E-3</v>
-      </c>
-      <c r="C741" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D741" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F741" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G741" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H741" s="1" t="s">
-        <v>415</v>
-      </c>
+      <c r="A741" s="1"/>
+      <c r="B741" s="1"/>
+      <c r="C741" s="1"/>
+      <c r="D741" s="1"/>
+      <c r="F741" s="1"/>
+      <c r="G741" s="8"/>
+      <c r="H741" s="1"/>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A742" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B742" s="1">
-        <v>0.20899999999999999</v>
-      </c>
-      <c r="C742" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D742" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F742" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G742" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H742" s="1" t="s">
-        <v>417</v>
-      </c>
+      <c r="A742" s="1"/>
+      <c r="B742" s="1"/>
+      <c r="C742" s="1"/>
+      <c r="D742" s="1"/>
+      <c r="F742" s="1"/>
+      <c r="G742" s="8"/>
+      <c r="H742" s="1"/>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A743" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B743" s="1">
-        <v>0.106</v>
-      </c>
-      <c r="C743" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D743" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F743" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G743" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H743" s="1" t="s">
-        <v>418</v>
-      </c>
+      <c r="A743" s="1"/>
+      <c r="B743" s="1"/>
+      <c r="C743" s="1"/>
+      <c r="D743" s="1"/>
+      <c r="F743" s="1"/>
+      <c r="G743" s="8"/>
+      <c r="H743" s="1"/>
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A744" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B744" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C744" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D744" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F744" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H744" s="1" t="s">
-        <v>416</v>
-      </c>
+      <c r="A744" s="1"/>
+      <c r="B744" s="1"/>
+      <c r="C744" s="1"/>
+      <c r="D744" s="1"/>
+      <c r="F744" s="1"/>
+      <c r="G744" s="8"/>
+      <c r="H744" s="1"/>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A745" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B745" s="1">
-        <v>2.3099999999999999E-5</v>
-      </c>
-      <c r="C745" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D745" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F745" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G745" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H745" s="1" t="s">
-        <v>419</v>
-      </c>
+      <c r="A745" s="1"/>
+      <c r="B745" s="1"/>
+      <c r="C745" s="1"/>
+      <c r="D745" s="1"/>
+      <c r="F745" s="1"/>
+      <c r="G745" s="8"/>
+      <c r="H745" s="1"/>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A746" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B746" s="1">
-        <v>7.64</v>
-      </c>
-      <c r="C746" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D746" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F746" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G746" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H746" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="A746" s="1"/>
+      <c r="B746" s="1"/>
+      <c r="C746" s="1"/>
+      <c r="D746" s="1"/>
+      <c r="F746" s="1"/>
+      <c r="G746" s="8"/>
+      <c r="H746" s="1"/>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A747" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B747" s="1">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="C747" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D747" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F747" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G747" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H747" s="1" t="s">
-        <v>420</v>
-      </c>
+      <c r="A747" s="1"/>
+      <c r="B747" s="1"/>
+      <c r="C747" s="1"/>
+      <c r="D747" s="1"/>
+      <c r="F747" s="1"/>
+      <c r="G747" s="8"/>
+      <c r="H747" s="1"/>
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A748" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B748" s="1">
-        <v>0.26700000000000002</v>
-      </c>
-      <c r="C748" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D748" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F748" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G748" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H748" s="1" t="s">
-        <v>421</v>
-      </c>
+      <c r="A748" s="1"/>
+      <c r="B748" s="1"/>
+      <c r="C748" s="1"/>
+      <c r="D748" s="1"/>
+      <c r="F748" s="1"/>
+      <c r="G748" s="8"/>
+      <c r="H748" s="1"/>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A749" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B749" s="1">
-        <v>2.14E-3</v>
-      </c>
-      <c r="C749" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D749" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F749" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G749" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H749" s="1" t="s">
-        <v>422</v>
-      </c>
+      <c r="A749" s="1"/>
+      <c r="B749" s="1"/>
+      <c r="C749" s="1"/>
+      <c r="D749" s="1"/>
+      <c r="F749" s="1"/>
+      <c r="G749" s="8"/>
+      <c r="H749" s="1"/>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A750" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B750" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="C750" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D750" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F750" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G750" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H750" s="1" t="s">
-        <v>423</v>
-      </c>
+      <c r="A750" s="1"/>
+      <c r="B750" s="1"/>
+      <c r="C750" s="1"/>
+      <c r="D750" s="1"/>
+      <c r="F750" s="1"/>
+      <c r="G750" s="8"/>
+      <c r="H750" s="1"/>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A751" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B751" s="1">
-        <v>1.06</v>
-      </c>
-      <c r="C751" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D751" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F751" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G751" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H751" s="1" t="s">
-        <v>424</v>
-      </c>
+      <c r="A751" s="1"/>
+      <c r="B751" s="1"/>
+      <c r="C751" s="1"/>
+      <c r="D751" s="1"/>
+      <c r="F751" s="1"/>
+      <c r="G751" s="8"/>
+      <c r="H751" s="1"/>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A752" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B752" s="1">
-        <v>14.7</v>
-      </c>
-      <c r="C752" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D752" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F752" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G752" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H752" s="1" t="s">
-        <v>425</v>
-      </c>
+      <c r="A752" s="1"/>
+      <c r="B752" s="1"/>
+      <c r="C752" s="1"/>
+      <c r="D752" s="1"/>
+      <c r="F752" s="1"/>
+      <c r="G752" s="8"/>
+      <c r="H752" s="1"/>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A753" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B753" s="1">
-        <v>0.249</v>
-      </c>
-      <c r="C753" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D753" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F753" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G753" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H753" s="1" t="s">
-        <v>418</v>
-      </c>
+      <c r="A753" s="1"/>
+      <c r="B753" s="1"/>
+      <c r="C753" s="1"/>
+      <c r="D753" s="1"/>
+      <c r="F753" s="1"/>
+      <c r="G753" s="8"/>
+      <c r="H753" s="1"/>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A754" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B754" s="1">
-        <v>0</v>
-      </c>
-      <c r="C754" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D754" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="F754" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G754" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H754" s="1" t="s">
-        <v>426</v>
-      </c>
+      <c r="A754" s="1"/>
+      <c r="B754" s="1"/>
+      <c r="C754" s="1"/>
+      <c r="D754" s="1"/>
+      <c r="F754" s="1"/>
+      <c r="G754" s="8"/>
+      <c r="H754" s="1"/>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A755" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B755" s="1">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="C755" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D755" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="F755" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G755" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H755" s="1" t="s">
-        <v>427</v>
-      </c>
+      <c r="A755" s="1"/>
+      <c r="B755" s="1"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
+      <c r="F755" s="1"/>
+      <c r="G755" s="8"/>
+      <c r="H755" s="1"/>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A756" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B756" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="C756" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D756" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F756" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G756" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H756" s="1" t="s">
-        <v>428</v>
-      </c>
+      <c r="A756" s="1"/>
+      <c r="B756" s="1"/>
+      <c r="C756" s="1"/>
+      <c r="D756" s="1"/>
+      <c r="F756" s="1"/>
+      <c r="G756" s="8"/>
+      <c r="H756" s="1"/>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A757" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B757" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="C757" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D757" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F757" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G757" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H757" s="1" t="s">
-        <v>429</v>
-      </c>
+      <c r="A757" s="1"/>
+      <c r="B757" s="1"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
+      <c r="F757" s="1"/>
+      <c r="G757" s="8"/>
+      <c r="H757" s="1"/>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A758" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B758" s="1">
-        <v>31.8</v>
-      </c>
-      <c r="C758" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D758" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F758" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G758" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H758" s="1" t="s">
-        <v>266</v>
-      </c>
+      <c r="A758" s="1"/>
+      <c r="B758" s="1"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
+      <c r="F758" s="1"/>
+      <c r="G758" s="8"/>
+      <c r="H758" s="1"/>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A759" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B759" s="1">
-        <v>3.0700000000000002E-2</v>
-      </c>
-      <c r="C759" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D759" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F759" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G759" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H759" s="1" t="s">
-        <v>430</v>
-      </c>
+      <c r="A759" s="1"/>
+      <c r="B759" s="1"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
+      <c r="F759" s="1"/>
+      <c r="G759" s="8"/>
+      <c r="H759" s="1"/>
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A760" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B760" s="1">
-        <v>-1.96</v>
-      </c>
-      <c r="C760" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D760" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F760" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G760" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H760" s="1" t="s">
-        <v>431</v>
-      </c>
+      <c r="A760" s="1"/>
+      <c r="B760" s="1"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
+      <c r="F760" s="1"/>
+      <c r="G760" s="8"/>
+      <c r="H760" s="1"/>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A761" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B761" s="1">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="C761" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D761" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F761" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G761" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H761" s="1" t="s">
-        <v>256</v>
-      </c>
+      <c r="A761" s="1"/>
+      <c r="B761" s="1"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
+      <c r="F761" s="1"/>
+      <c r="G761" s="8"/>
+      <c r="H761" s="1"/>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A762" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B762" s="1">
-        <v>-1.84E-2</v>
-      </c>
-      <c r="C762" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D762" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F762" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G762" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H762" s="1" t="s">
-        <v>432</v>
-      </c>
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
+      <c r="F762" s="1"/>
+      <c r="G762" s="8"/>
+      <c r="H762" s="1"/>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A763" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B763" s="1">
-        <v>1.7599999999999999E-8</v>
-      </c>
-      <c r="C763" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D763" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F763" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G763" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H763" s="1" t="s">
-        <v>433</v>
-      </c>
+      <c r="A763" s="1"/>
+      <c r="B763" s="1"/>
+      <c r="C763" s="1"/>
+      <c r="D763" s="1"/>
+      <c r="F763" s="1"/>
+      <c r="G763" s="8"/>
+      <c r="H763" s="1"/>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A764" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B764" s="1">
-        <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="C764" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D764" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F764" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G764" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H764" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="A764" s="1"/>
+      <c r="B764" s="1"/>
+      <c r="C764" s="1"/>
+      <c r="D764" s="1"/>
+      <c r="F764" s="1"/>
+      <c r="G764" s="8"/>
+      <c r="H764" s="1"/>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A765" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B765" s="1">
-        <v>1.84E-2</v>
-      </c>
-      <c r="C765" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D765" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F765" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G765" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H765" s="1" t="s">
-        <v>434</v>
-      </c>
+      <c r="A765" s="1"/>
+      <c r="B765" s="1"/>
+      <c r="C765" s="1"/>
+      <c r="D765" s="1"/>
+      <c r="F765" s="1"/>
+      <c r="G765" s="8"/>
+      <c r="H765" s="1"/>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A766" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B766" s="1">
-        <v>5.58</v>
-      </c>
-      <c r="C766" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D766" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F766" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G766" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H766" s="1" t="s">
-        <v>435</v>
-      </c>
+      <c r="A766" s="1"/>
+      <c r="B766" s="1"/>
+      <c r="C766" s="1"/>
+      <c r="D766" s="1"/>
+      <c r="F766" s="1"/>
+      <c r="G766" s="8"/>
+      <c r="H766" s="1"/>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A767" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B767" s="1">
-        <v>0.44700000000000001</v>
-      </c>
-      <c r="C767" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D767" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F767" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G767" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H767" s="1" t="s">
-        <v>435</v>
-      </c>
+      <c r="A767" s="1"/>
+      <c r="B767" s="1"/>
+      <c r="C767" s="1"/>
+      <c r="D767" s="1"/>
+      <c r="F767" s="1"/>
+      <c r="G767" s="8"/>
+      <c r="H767" s="1"/>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A768" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B768" s="1">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="C768" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D768" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F768" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G768" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H768" s="1" t="s">
-        <v>436</v>
-      </c>
+      <c r="A768" s="1"/>
+      <c r="B768" s="1"/>
+      <c r="C768" s="1"/>
+      <c r="D768" s="1"/>
+      <c r="F768" s="1"/>
+      <c r="G768" s="8"/>
+      <c r="H768" s="1"/>
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A769" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B769" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="C769" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D769" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F769" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G769" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H769" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="A769" s="1"/>
+      <c r="B769" s="1"/>
+      <c r="C769" s="1"/>
+      <c r="D769" s="1"/>
+      <c r="F769" s="1"/>
+      <c r="G769" s="8"/>
+      <c r="H769" s="1"/>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A770" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B770" s="1">
-        <v>7.3299999999999997E-3</v>
-      </c>
-      <c r="C770" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D770" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F770" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G770" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H770" s="1" t="s">
-        <v>437</v>
-      </c>
+      <c r="A770" s="1"/>
+      <c r="B770" s="1"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
+      <c r="F770" s="1"/>
+      <c r="G770" s="8"/>
+      <c r="H770" s="1"/>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A771" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B771" s="1">
-        <v>1.7899999999999999E-3</v>
-      </c>
-      <c r="C771" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D771" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F771" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G771" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H771" s="1" t="s">
-        <v>438</v>
-      </c>
+      <c r="A771" s="1"/>
+      <c r="B771" s="1"/>
+      <c r="C771" s="1"/>
+      <c r="D771" s="1"/>
+      <c r="F771" s="1"/>
+      <c r="G771" s="8"/>
+      <c r="H771" s="1"/>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A772" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B772" s="1">
-        <v>7.64</v>
-      </c>
-      <c r="C772" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D772" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F772" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G772" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H772" s="1" t="s">
-        <v>398</v>
-      </c>
+      <c r="A772" s="1"/>
+      <c r="B772" s="1"/>
+      <c r="C772" s="1"/>
+      <c r="D772" s="1"/>
+      <c r="F772" s="1"/>
+      <c r="G772" s="8"/>
+      <c r="H772" s="1"/>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A773" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B773" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="C773" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D773" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F773" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G773" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H773" s="1" t="s">
-        <v>399</v>
-      </c>
+      <c r="A773" s="1"/>
+      <c r="B773" s="1"/>
+      <c r="C773" s="1"/>
+      <c r="D773" s="1"/>
+      <c r="F773" s="1"/>
+      <c r="G773" s="8"/>
+      <c r="H773" s="1"/>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A774" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B774" s="1">
-        <v>1.54E-2</v>
-      </c>
-      <c r="C774" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D774" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F774" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G774" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H774" s="1" t="s">
-        <v>439</v>
-      </c>
+      <c r="A774" s="1"/>
+      <c r="B774" s="1"/>
+      <c r="C774" s="1"/>
+      <c r="D774" s="1"/>
+      <c r="F774" s="1"/>
+      <c r="G774" s="8"/>
+      <c r="H774" s="1"/>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A775" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B775" s="1">
-        <v>6.4299999999999996E-2</v>
-      </c>
-      <c r="C775" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D775" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F775" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G775" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H775" s="1" t="s">
-        <v>440</v>
-      </c>
+      <c r="A775" s="1"/>
+      <c r="B775" s="1"/>
+      <c r="C775" s="1"/>
+      <c r="D775" s="1"/>
+      <c r="F775" s="1"/>
+      <c r="G775" s="8"/>
+      <c r="H775" s="1"/>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A776" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B776" s="1">
-        <v>6.6900000000000001E-2</v>
-      </c>
-      <c r="C776" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D776" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F776" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G776" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H776" s="1" t="s">
-        <v>441</v>
-      </c>
+      <c r="A776" s="1"/>
+      <c r="B776" s="1"/>
+      <c r="C776" s="1"/>
+      <c r="D776" s="1"/>
+      <c r="F776" s="1"/>
+      <c r="G776" s="8"/>
+      <c r="H776" s="1"/>
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A777" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B777" s="1">
-        <v>-2.06E-2</v>
-      </c>
-      <c r="C777" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D777" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F777" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G777" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H777" s="1" t="s">
-        <v>269</v>
-      </c>
+      <c r="A777" s="1"/>
+      <c r="B777" s="1"/>
+      <c r="C777" s="1"/>
+      <c r="D777" s="1"/>
+      <c r="F777" s="1"/>
+      <c r="G777" s="8"/>
+      <c r="H777" s="1"/>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A778" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B778" s="1">
-        <v>-0.38900000000000001</v>
-      </c>
-      <c r="C778" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D778" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F778" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G778" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H778" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="A778" s="1"/>
+      <c r="B778" s="1"/>
+      <c r="C778" s="1"/>
+      <c r="D778" s="1"/>
+      <c r="F778" s="1"/>
+      <c r="G778" s="8"/>
+      <c r="H778" s="1"/>
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A779" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="B779" s="1">
-        <v>-2.91</v>
-      </c>
-      <c r="C779" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D779" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F779" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G779" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H779" s="1" t="s">
-        <v>443</v>
-      </c>
+      <c r="A779" s="1"/>
+      <c r="B779" s="1"/>
+      <c r="C779" s="1"/>
+      <c r="D779" s="1"/>
+      <c r="F779" s="1"/>
+      <c r="G779" s="8"/>
+      <c r="H779" s="1"/>
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A780" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B780" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="C780" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D780" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F780" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G780" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H780" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="A780" s="1"/>
+      <c r="B780" s="1"/>
+      <c r="C780" s="1"/>
+      <c r="D780" s="1"/>
+      <c r="F780" s="1"/>
+      <c r="G780" s="8"/>
+      <c r="H780" s="1"/>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G781" s="8"/>
@@ -19240,6 +18515,5165 @@
         </is>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1000">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=CSD19536KCS;firstvariant;materialmg={'Aluminum': 2.078818, 'Nickel': 0.000671, 'Silicon': 4e-06, 'Lead': 16.43543, 'Tin': 170.8789, 'Silver': 0.26367, 'Copper': 1367.945, 'Iron': 1.644, 'Phosphorus': 0.411, 'Silica': 395.438103, 'Metal Hydroxide': 42.368368, 'Carbon Black': 2.824558, 'Epoxy': 124.280547, 'Doped Silicon': 19.851772};unknownkg={'Metal Hydroxide': 4.2368368e-05}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1007">
+        <v>1</v>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1008">
+        <v>2.078818e-06</v>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1009">
+        <v>6.710000000000001e-10</v>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1010">
+        <v>4e-12</v>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1011">
+        <v>1.643543e-05</v>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1012">
+        <v>0.0001708789</v>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1013">
+        <v>2.6367000000000003e-07</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1014">
+        <v>0.001367945</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1015">
+        <v>1.6439999999999998e-06</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1016">
+        <v>4.1099999999999996e-07</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1017">
+        <v>0.000395438103</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1018">
+        <v>2.824558e-06</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1019">
+        <v>0.000124280547</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1020">
+        <v>1.9851772000000002e-05</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1021">
+        <v>0.002144420841</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1026">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=UCC27524AQDRQ1;firstvariant;materialmg={'Yttrium': 1e-06, 'Gold': 0.161614, 'Silver': 0.183922, 'Epoxy': 6.3863900000000005, 'Copper': 12.8106, 'Iron': 0.3432, 'Phosphorus': 0.0198, 'Zinc': 0.0264, 'Nickel': 0.09512, 'Palladium': 0.0041, 'Phenolic Resin': 2.11347, 'Fused Silica': 51.629055, 'Carbon Black': 0.301924, 'Doped Silicon': 0.75243};unknownkg={}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1033">
+        <v>1</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>market for yttrium oxide</t>
+        </is>
+      </c>
+      <c r="B1034">
+        <v>1.2699316490345291e-12</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>yttrium oxide</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>yttrium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1035">
+        <v>1.61614e-07</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1036">
+        <v>1.83922e-07</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1037">
+        <v>6.3863900000000005e-06</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1038">
+        <v>1.28106e-05</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1039">
+        <v>3.432e-07</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1040">
+        <v>1.9800000000000002e-08</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1041">
+        <v>2.64e-08</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1042">
+        <v>9.512e-08</v>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1043">
+        <v>4.1e-09</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>market for phenolic resin</t>
+        </is>
+      </c>
+      <c r="B1044">
+        <v>2.1134699999999998e-06</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>phenolic resin</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>phenolic resin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1045">
+        <v>5.1629055e-05</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1046">
+        <v>3.0192400000000005e-07</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1047">
+        <v>7.524300000000001e-07</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1048">
+        <v>7.482802600000001e-05</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1053">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=TMS320F28035PNT;firstvariant;materialmg={'Aluminum': 1e-06, 'Copper': 240.17908, 'Iron': 5.783354, 'Proprietary Materials': 4.7e-05, 'Gold': 0.033028, 'Palladium': 0.166628, 'Silver': 2.7728189999999997, 'Epoxy': 42.136409, 'Phosphorus': 0.203033, 'Lead': 0.036915, 'Zinc': 0.307625, 'Nickel': 3.469026, 'Fused Silica': 309.998135, 'Carbon Black': 1.056812, 'Chlorine': 0.003523, 'Doped Silicon': 14.182021};unknownkg={'Proprietary Materials': 4.7e-11}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1060">
+        <v>1</v>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1061">
+        <v>1e-12</v>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1062">
+        <v>0.00024017908</v>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1063">
+        <v>5.783354e-06</v>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1064">
+        <v>3.3028e-08</v>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1065">
+        <v>1.66628e-07</v>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1066">
+        <v>2.772819e-06</v>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1067">
+        <v>4.2136409e-05</v>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1068">
+        <v>2.03033e-07</v>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1069">
+        <v>3.6915000000000003e-08</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1070">
+        <v>3.07625e-07</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1071">
+        <v>3.469026e-06</v>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1072">
+        <v>0.00030999813499999997</v>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1073">
+        <v>1.0568120000000001e-06</v>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B1074">
+        <v>3.523e-09</v>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1075">
+        <v>1.4182021e-05</v>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1076">
+        <v>0.000620328456</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1081">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 2.6459999999999997e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 5.601e-06, 'carbon': 2.0046e-05, 'epoxy': 0.00038086799999999997, 'silica': 0.0016036569999999999, 'Sn': 3.2692e-05, 'Ni': 2.9065e-05, 'Sb': 1.26e-07, 'Ag': 3.14e-07}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="B1088">
+        <v>1</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B1089">
+        <v>2.6459999999999997e-06</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1090">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1091">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1092">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1093">
+        <v>5.601e-06</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1094">
+        <v>2.0046e-05</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1095">
+        <v>0.00038086799999999997</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1096">
+        <v>0.0016036569999999999</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1097">
+        <v>3.2692e-05</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1098">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1099">
+        <v>1.26e-07</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1100">
+        <v>3.14e-07</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1101">
+        <v>0.006047253</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 4.941e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 4.257e-06, 'carbon': 2.0032e-05, 'epoxy': 0.000380613, 'silica': 0.00160258, 'Sn': 3.3233e-05, 'Ni': 2.9065e-05, 'Sb': 2.0899999999999998e-07, 'Ag': 5.23e-07}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="B1113">
+        <v>1</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B1114">
+        <v>4.941e-06</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1115">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1116">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1117">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1118">
+        <v>4.257e-06</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1119">
+        <v>2.0032e-05</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1120">
+        <v>0.000380613</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1121">
+        <v>0.00160258</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1122">
+        <v>3.3233e-05</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1123">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1124">
+        <v>2.0899999999999998e-07</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1125">
+        <v>5.23e-07</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1126">
+        <v>0.006047690999999999</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. UCC21710firstMCDvarianthttps://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1;manufacturerledger={'Copper': 309.564275, 'Nickel': 0.168363, 'Proprietary Materials': 1.5e-05, 'Gold': 0.0014520000000000002, 'Palladium': 0.010566, 'Silver': 0.9804740000000001, 'Epoxy': 37.038359, 'Iron': 7.4636, 'Phosphorus': 0.26202, 'Lead': 0.04764, 'Zinc': 0.397, 'Fused Silica': 328.633964, 'Carbon Black': 1.835944, 'Chlorine': 0.007344, 'Doped Silicon': 6.823678}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1138">
+        <v>1</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1139">
+        <v>0.000309564275</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1140">
+        <v>1.68363e-07</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1141">
+        <v>1.4520000000000002e-09</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1142">
+        <v>1.0566e-08</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1143">
+        <v>9.80474e-07</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1144">
+        <v>3.7038359e-05</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1145">
+        <v>7.463599999999999e-06</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1146">
+        <v>2.6201999999999996e-07</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1147">
+        <v>4.764e-08</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1148">
+        <v>3.97e-07</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1149">
+        <v>0.000328633964</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1150">
+        <v>1.835944e-06</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B1151">
+        <v>7.3439999999999995e-09</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1152">
+        <v>6.823678e-06</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+ BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Finishednominalmass=18.491259364830004kg;bulkledger={'Al': 7.64, 'Cu': 3.06, 'steel': 1.45, 'PP': 1.41, 'electrolytic': 0.412, 'film': 0.267, 'ferrite': 2.16, 'PCB': 1.6940000000000002, 'resistors': 0.01, 'diodes': 0.01, 'connectors': 0.01};packagecounts={'CSD19536KCS': 126, 'UCC27524AQDRQ1': 72, 'TMS320F28035PNT': 19, '650V': 6, '1200V': 6, 'ACdriver': 12};nominalpackagemasses={'CSD19536KCS': 0.002144420841, 'UCC27524AQDRQ1': 7.482802600000001e-05, 'TMS320F28035PNT': 0.000620328456, '650V': 0.006047253, '1200V': 0.006047690999999999, 'ACdriver': 0.000693234694}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+      <c r="B1164">
+        <v>1</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1165">
+        <v>126</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1166">
+        <v>72</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="B1167">
+        <v>19</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="B1168">
+        <v>6</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="B1169">
+        <v>6</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1170">
+        <v>12</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>market for aluminium, cast alloy</t>
+        </is>
+      </c>
+      <c r="B1171">
+        <v>7.64</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>aluminium, cast alloy</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>aluminium, cast alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1172">
+        <v>3.06</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1173">
+        <v>1.45</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1174">
+        <v>1.41</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>market for capacitor, electrolyte type, &gt; 2cm height</t>
+        </is>
+      </c>
+      <c r="B1175">
+        <v>0.412</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>capacitor, electrolyte type, &gt; 2cm height</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>capacitor, electrolyte type, &gt; 2cm height</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1176">
+        <v>0.267</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B1177">
+        <v>2.16</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+      <c r="B1178">
+        <v>0.55</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B1179">
+        <v>0.01</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>diode production, glass-, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="B1180">
+        <v>0.01</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>diode, glass-, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>diode, glass-, for surface-mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>market for electric connector, wire clamp</t>
+        </is>
+      </c>
+      <c r="B1181">
+        <v>0.01</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>electric connector, wire clamp</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>electric connector, wire clamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="B1182">
+        <v>3.06</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+      <c r="B1183">
+        <v>7.64</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="B1184">
+        <v>1.45</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1185">
+        <v>16.9</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1186">
+        <v>5.72</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+      <c r="B1187">
+        <v>0.361</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, other than natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B1188">
+        <v>2.91</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>market for packaging film, low density polyethylene</t>
+        </is>
+      </c>
+      <c r="B1189">
+        <v>0.0184</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>packaging film, low density polyethylene</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>packaging film, low density polyethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>market for waste paperboard, unsorted</t>
+        </is>
+      </c>
+      <c r="B1190">
+        <v>-2.91</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>waste paperboard, unsorted</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>waste paperboard, unsorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>market for waste polyethylene</t>
+        </is>
+      </c>
+      <c r="B1191">
+        <v>-0.0184</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>waste polyethylene</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>waste polyethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B1192">
+        <v>-18.491259364830004</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -15085,8 +15085,12 @@
       <c r="A809" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B809" s="1" t="s">
-        <v>472</v>
+      <c r="B809" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED QAPS WASTEWATER DIRECTION, issue110,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, inherited QAPS alkalization inventory; actual native ecoinvent3.8-3.12 negative-reference wastewater treatment suppliers checked read-only. This process supplies1kg alkalized membrane and produces.0201m3 wastewater for treatment. Existing technosphere+.0201m3 points to treatment supplier whose production exchange is-1m3 wastewater; it solves asnegative treatment activity and credits treatment burdens. Correct input to-.0201m3, preserving physical volume,unit,supplierlocation EuropewithoutSwitzerland andall reagent/water/energy/polymer quantities. At FU1kg membrane the immediate wastewater-treatment supply is now+.0201 rather than-.0201 activityunits. Adjacent quaternization/chloromethylation wastewater exchanges alreadynegative andunchanged. No new water-volumeestimate,metalrecoverycredit,primary/secondarysplit or full membrane-recipe validation. Nonunit upstream batch yields remain correctly in their own production amounts. Scope one existingworkbook,one signedamount anddocumentation;no runtime/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
       <c r="C809"/>
       <c r="D809"/>
@@ -15206,7 +15210,11 @@
       <c r="G816" t="s">
         <v>8</v>
       </c>
-      <c r="H816"/>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
       <c r="J816"/>
     </row>
     <row r="817" spans="1:10" x14ac:dyDescent="0.2">
@@ -15231,7 +15239,11 @@
       <c r="G817" t="s">
         <v>551</v>
       </c>
-      <c r="H817"/>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>APPROVED QAPS WASTEWATER DIRECTION, issue110,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, inherited QAPS alkalization inventory; actual native ecoinvent3.8-3.12 negative-reference wastewater treatment suppliers checked read-only. This process supplies1kg alkalized membrane and produces.0201m3 wastewater for treatment. Existing technosphere+.0201m3 points to treatment supplier whose production exchange is-1m3 wastewater; it solves asnegative treatment activity and credits treatment burdens. Correct input to-.0201m3, preserving physical volume,unit,supplierlocation EuropewithoutSwitzerland andall reagent/water/energy/polymer quantities. At FU1kg membrane the immediate wastewater-treatment supply is now+.0201 rather than-.0201 activityunits. Adjacent quaternization/chloromethylation wastewater exchanges alreadynegative andunchanged. No new water-volumeestimate,metalrecoverycredit,primary/secondarysplit or full membrane-recipe validation. Nonunit upstream batch yields remain correctly in their own production amounts. Scope one existingworkbook,one signedamount anddocumentation;no runtime/native edits.</t>
+        </is>
+      </c>
       <c r="J817"/>
     </row>
     <row r="818" spans="1:10" x14ac:dyDescent="0.2">
@@ -15414,7 +15426,7 @@
         <v>560</v>
       </c>
       <c r="B825">
-        <v>2.01E-2</v>
+        <v>-0.0201</v>
       </c>
       <c r="C825" t="s">
         <v>36</v>
@@ -15431,7 +15443,11 @@
       <c r="G825" t="s">
         <v>448</v>
       </c>
-      <c r="H825"/>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>APPROVED QAPS WASTEWATER DIRECTION, issue110,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, inherited QAPS alkalization inventory; actual native ecoinvent3.8-3.12 negative-reference wastewater treatment suppliers checked read-only. This process supplies1kg alkalized membrane and produces.0201m3 wastewater for treatment. Existing technosphere+.0201m3 points to treatment supplier whose production exchange is-1m3 wastewater; it solves asnegative treatment activity and credits treatment burdens. Correct input to-.0201m3, preserving physical volume,unit,supplierlocation EuropewithoutSwitzerland andall reagent/water/energy/polymer quantities. At FU1kg membrane the immediate wastewater-treatment supply is now+.0201 rather than-.0201 activityunits. Adjacent quaternization/chloromethylation wastewater exchanges alreadynegative andunchanged. No new water-volumeestimate,metalrecoverycredit,primary/secondarysplit or full membrane-recipe validation. Nonunit upstream batch yields remain correctly in their own production amounts. Scope one existingworkbook,one signedamount anddocumentation;no runtime/native edits.</t>
+        </is>
+      </c>
       <c r="J825"/>
     </row>
     <row r="827" spans="1:10" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -13282,8 +13282,15 @@
       <c r="A649" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B649" s="1" t="s">
-        <v>472</v>
+      <c r="B649" s="1" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY PUMP SPECIFICATION AUDIT, issue122, 2026-10-19. Zhang2025 DOI10.1039/D4EB00027G. Iwaki MX European manual, pp8,11, manufacturer reference https://www.iwaki.be/wp-content/uploads/2020/10/MX-250-505_T480-7_Europe.pdf : MX400 shaft0.37kW,6.2kg excluding motor; glass-reinforcedPP, ferrite, Al alloy, cast iron, stainless fasteners, alumina, PTFE, PPS and elastomer components. It publishes material identities but not their individual masses.
+UNRESOLVED EQUIPMENT/MATERIAL PROXY: one nominal500W pump is represented by2.5641025641025643 complete40W solar-circulation pumps. This is a mass scaling (native approximately3.9kg each -&gt;10kg), NOT proof a real102.56W pump is installed and NOT justification for multiplying material use by500/40. Retain two installed pumps per system and existing operating electricity until a hydraulic duty and input-power basis are established.
+The recovered chemical-pump reference establishes appropriate separate motor/wetted-part concepts, but is not a matched500W electrical-input/10kg product or a measured RFB design. MX400 has370W shaft rating,6.2kg WITHOUT motor; do not confuse shaft power with electrical input or use pump-only mass for the whole unit. Its ferrite magnetic coupling is not evidence of zero rare-earths in every alternative pump. Exact fluid compatibility requires electrolyte composition, pH, chloride concentration, density, temperature, required flow/head and seal variant; a generic stainless solar pump is unvalidated for those duties.
+No source recovered individual material masses, matching motor mass/efficiency, manufacturer service life or required replacement schedule. Leave numerical coefficients unchanged rather than invent an elemental split or scale by rated watts. Required replacement inventory must include dry motor, housing/impeller, magnetic coupling, ceramics/seals and lifetime, with explicit unknown residual composition. Operating losses already lie within system roundtrip-efficiency reference and must not be charged twice. Numerical correction remains OPEN; this is a targeted evidence/coverage record, not a certified500W pump inventory. No native/runtime/share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.2">
@@ -13321,6 +13328,11 @@
       <c r="G652" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A653" s="1" t="s">
@@ -13344,6 +13356,14 @@
       <c r="G653" s="2" t="s">
         <v>534</v>
       </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY PUMP SPECIFICATION AUDIT, issue122, 2026-10-19. Zhang2025 DOI10.1039/D4EB00027G. Iwaki MX European manual, pp8,11, manufacturer reference https://www.iwaki.be/wp-content/uploads/2020/10/MX-250-505_T480-7_Europe.pdf : MX400 shaft0.37kW,6.2kg excluding motor; glass-reinforcedPP, ferrite, Al alloy, cast iron, stainless fasteners, alumina, PTFE, PPS and elastomer components. It publishes material identities but not their individual masses.
+UNRESOLVED EQUIPMENT/MATERIAL PROXY: one nominal500W pump is represented by2.5641025641025643 complete40W solar-circulation pumps. This is a mass scaling (native approximately3.9kg each -&gt;10kg), NOT proof a real102.56W pump is installed and NOT justification for multiplying material use by500/40. Retain two installed pumps per system and existing operating electricity until a hydraulic duty and input-power basis are established.
+The recovered chemical-pump reference establishes appropriate separate motor/wetted-part concepts, but is not a matched500W electrical-input/10kg product or a measured RFB design. MX400 has370W shaft rating,6.2kg WITHOUT motor; do not confuse shaft power with electrical input or use pump-only mass for the whole unit. Its ferrite magnetic coupling is not evidence of zero rare-earths in every alternative pump. Exact fluid compatibility requires electrolyte composition, pH, chloride concentration, density, temperature, required flow/head and seal variant; a generic stainless solar pump is unvalidated for those duties.
+No source recovered individual material masses, matching motor mass/efficiency, manufacturer service life or required replacement schedule. Leave numerical coefficients unchanged rather than invent an elemental split or scale by rated watts. Required replacement inventory must include dry motor, housing/impeller, magnetic coupling, ceramics/seals and lifetime, with explicit unknown residual composition. Operating losses already lie within system roundtrip-efficiency reference and must not be charged twice. Numerical correction remains OPEN; this is a targeted evidence/coverage record, not a certified500W pump inventory. No native/runtime/share changes.</t>
+        </is>
+      </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A654" s="1" t="s">
@@ -13366,6 +13386,14 @@
       </c>
       <c r="G654" s="1" t="s">
         <v>351</v>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>APPROVED FLOW-BATTERY PUMP SPECIFICATION AUDIT, issue122, 2026-10-19. Zhang2025 DOI10.1039/D4EB00027G. Iwaki MX European manual, pp8,11, manufacturer reference https://www.iwaki.be/wp-content/uploads/2020/10/MX-250-505_T480-7_Europe.pdf : MX400 shaft0.37kW,6.2kg excluding motor; glass-reinforcedPP, ferrite, Al alloy, cast iron, stainless fasteners, alumina, PTFE, PPS and elastomer components. It publishes material identities but not their individual masses.
+UNRESOLVED EQUIPMENT/MATERIAL PROXY: one nominal500W pump is represented by2.5641025641025643 complete40W solar-circulation pumps. This is a mass scaling (native approximately3.9kg each -&gt;10kg), NOT proof a real102.56W pump is installed and NOT justification for multiplying material use by500/40. Retain two installed pumps per system and existing operating electricity until a hydraulic duty and input-power basis are established.
+The recovered chemical-pump reference establishes appropriate separate motor/wetted-part concepts, but is not a matched500W electrical-input/10kg product or a measured RFB design. MX400 has370W shaft rating,6.2kg WITHOUT motor; do not confuse shaft power with electrical input or use pump-only mass for the whole unit. Its ferrite magnetic coupling is not evidence of zero rare-earths in every alternative pump. Exact fluid compatibility requires electrolyte composition, pH, chloride concentration, density, temperature, required flow/head and seal variant; a generic stainless solar pump is unvalidated for those duties.
+No source recovered individual material masses, matching motor mass/efficiency, manufacturer service life or required replacement schedule. Leave numerical coefficients unchanged rather than invent an elemental split or scale by rated watts. Required replacement inventory must include dry motor, housing/impeller, magnetic coupling, ceramics/seals and lifetime, with explicit unknown residual composition. Operating losses already lie within system roundtrip-efficiency reference and must not be charged twice. Numerical correction remains OPEN; this is a targeted evidence/coverage record, not a certified500W pump inventory. No native/runtime/share changes.</t>
+        </is>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -6057,7 +6057,7 @@
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode production, casting and rolling</t>
         </is>
       </c>
       <c r="B232" s="1">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="G232" s="1" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode, casting and rolling</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA production</t>
         </is>
       </c>
       <c r="B381">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
         </is>
       </c>
     </row>
@@ -13883,7 +13883,7 @@
     <row r="696" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A696" s="1" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate production, flow battery end plate</t>
         </is>
       </c>
       <c r="B696" s="1">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="G696" s="1" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate, flow battery end plate</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14228,7 @@
     <row r="725" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A725" s="1" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter production, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
       <c r="B725" s="1">
@@ -14253,7 +14253,7 @@
       <c r="G725" s="1"/>
       <c r="H725" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst production, 10% palladium on activated carbon</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17463,8 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: palladium on activated carbon, 10wtpercent, synthesis engineering reference. Former reference product: palladium on activated carbon, 10wtpercent, synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17525,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst production, 10% palladium on activated carbon</t>
         </is>
       </c>
       <c r="B945">
@@ -17547,12 +17548,12 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon</t>
         </is>
       </c>
     </row>
@@ -17704,7 +17705,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA production</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17739,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17775,8 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Former reference product: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17837,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA production</t>
         </is>
       </c>
       <c r="B961">
@@ -17858,19 +17860,19 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference</t>
+          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst production, 10% palladium on activated carbon</t>
         </is>
       </c>
       <c r="B962">
@@ -17893,12 +17895,12 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>palladium on activated carbon, 10wtpercent, synthesis engineering reference</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17947,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate production, flow battery end plate</t>
         </is>
       </c>
     </row>
@@ -17979,7 +17981,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate, flow battery end plate</t>
         </is>
       </c>
     </row>
@@ -18015,7 +18017,8 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BULK Al END-PLATE SUPPLY, issue81,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Source design uses aluminium endplates; workbook specifies10mm thickness but buys batterycurrentcollectorfoil. Replace that supplier at the same1kg finishedplate/kg endplate with a scopedbulkplate reference: genericwroughtAl supply,aluminium sheet/plate rolling service and averageAl product finishing service. No additional lithium-ion battery,highpuritycollector architecture orAlLi alloy is required. Preserve installedHFB49.49331859090909kg andOFB26.731447961538468kg endplates, existingarea/count and nominal40kWh design. Actual plate alloy is unspecified; use the genericwroughtalloy supplymix as a declared forming-compatible proxy, not a certified6061plate or pureprimaryAl claim.95% totalmetalretention is an explicitengineeringassumption,test90-100%; buy1/0.95kgAl and matchinggrossrolling service,finish1kg netplate,dispose1/0.95-1kg mixed manufacturingoffcut. Native metalworking services exclude the separately requiredmetal feed; do not treat servicekg as anotherkg retainedAl. Generic hazardous-incineration is a manufacturingloss-fate proxy,not an endorsed commercialAlscrap route or an addedrecoverycredit. Actual net/gross dimensions,drilledholes,bolting tolerance,alloyingcomposition,processingyield and futureweight reduction need engineeringverification. This change replaces a foilmanufacturing proxy; it does not assert the finishedplate masses are optimized or sourcefullyreproduced. No separatefullsystemreplacement or duplicatedplate purchase. Preserve source exclusionofbatteryEOL and all other subsystemrecipes; no native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: aluminium plate, flow-battery end plate, engineering reference. Former reference product: aluminium plate, flow-battery end plate, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BULK Al END-PLATE SUPPLY, issue81,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Source design uses aluminium endplates; workbook specifies10mm thickness but buys batterycurrentcollectorfoil. Replace that supplier at the same1kg finishedplate/kg endplate with a scopedbulkplate reference: genericwroughtAl supply,aluminium sheet/plate rolling service and averageAl product finishing service. No additional lithium-ion battery,highpuritycollector architecture orAlLi alloy is required. Preserve installedHFB49.49331859090909kg andOFB26.731447961538468kg endplates, existingarea/count and nominal40kWh design. Actual plate alloy is unspecified; use the genericwroughtalloy supplymix as a declared forming-compatible proxy, not a certified6061plate or pureprimaryAl claim.95% totalmetalretention is an explicitengineeringassumption,test90-100%; buy1/0.95kgAl and matchinggrossrolling service,finish1kg netplate,dispose1/0.95-1kg mixed manufacturingoffcut. Native metalworking services exclude the separately requiredmetal feed; do not treat servicekg as anotherkg retainedAl. Generic hazardous-incineration is a manufacturingloss-fate proxy,not an endorsed commercialAlscrap route or an addedrecoverycredit. Actual net/gross dimensions,drilledholes,bolting tolerance,alloyingcomposition,processingyield and futureweight reduction need engineeringverification. This change replaces a foilmanufacturing proxy; it does not assert the finishedplate masses are optimized or sourcefullyreproduced. No separatefullsystemreplacement or duplicatedplate purchase. Preserve source exclusionofbatteryEOL and all other subsystemrecipes; no native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -18076,7 +18079,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate production, flow battery end plate</t>
         </is>
       </c>
       <c r="B975">
@@ -18099,12 +18102,12 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate, flow battery end plate</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>aluminium plate, flow-battery end plate, engineering reference</t>
+          <t xml:space="preserve">aluminium plate, flow battery end plate</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18259,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode production, casting and rolling</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18293,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode, casting and rolling</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18329,8 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>APPROVED ZINC-FOIL PROCESS IDENTITY, issue82,2026-10-18. Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition. Replace the active HFB zincfelt proxy,which boughtAlcastingfacility andCusheetrolling,by a distinct1kg netpure-Zn foil reference. Retain HFBinstalledZn electrode4.94kg and all existing stackcellarea/count; do not infer porousfelt volume,density or morphology. Retained metal is1kgZn,not addedCu/Al merelybecause former processproxies namedthosemetals. Use existingrefinedZn marketat1/0.95kg,explicit95% totalcasting/rollingretention,test90-100%,matched1/0.95-1kg manufacturingresidue. Use an electricinduction melting/casting+rolling engineeringroute: zincspecificheat0.388kJ/kgK,latentheat112kJ/kg,reference20-25Cfeedheatedto500C,idealheat0.2963MJ/kg;50% melterefficiency and0.05kWh/kg rollingallowance give0.22590643274853806kWh/kg netfoil. These thermalconstants andselectedefficiency/rollingelectricity are engineeringreferences,not a measured electrodefoilline. Testmelterefficiency30-80%,rolling0.01-0.1kWh/kg andyield90-100%. Do not read EPD cumulativeA1-A3 environmentalenergyindicators as processfuel consumption,which would doublecountrefinedZnproduction. Transfer only its documentedprocessarchitecture and0.08g/kg lubricant coefficient; do not transferbuildingalloyCu/Ti additions,coating,longbuildinglife or moduleDcredits. Genericlubricatingoil is the emulsion-supplyproxy;coolingwater,emulsiondilution,highpuritypowder/foilprocessing,surfacepreparation andfactoryequipmentareunresolved. Manufacturingwaste usesmixedhazardoustreatment proxy without inventedZnrecoverycredit. Legacyfeltprovider remainsavailable but theHFB stackbuys only the newfoilreference at unchangedmass. Metalcharacterization mustfollowrealZn feed,not a copper-shapingservice. No native,runtime,YAML edits or primary-secondaryshare changes.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: zinc foil electrode, casting and rolling engineering reference. Former reference product: zinc foil electrode, casting and rolling engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ZINC-FOIL PROCESS IDENTITY, issue82,2026-10-18. Zhang2025 Table1 identifies zincfoil,notporousfelt. RHEINZINK CLASSIC EPD2024-2029 describes inductionmelting500-550C,casting,rolling andlubricant0.08kg/tonne: https://www.rheinzink.com/fileadmin/redaktion/RHEINZINK_GLOBAL/Downloads/Technical-Documents/epd_rheinzink-classic_bright-rolled_2024-2029.pdf . Its building-productZn-Cu-Tialloy is NOT copied as electrodecomposition. Replace the active HFB zincfelt proxy,which boughtAlcastingfacility andCusheetrolling,by a distinct1kg netpure-Zn foil reference. Retain HFBinstalledZn electrode4.94kg and all existing stackcellarea/count; do not infer porousfelt volume,density or morphology. Retained metal is1kgZn,not addedCu/Al merelybecause former processproxies namedthosemetals. Use existingrefinedZn marketat1/0.95kg,explicit95% totalcasting/rollingretention,test90-100%,matched1/0.95-1kg manufacturingresidue. Use an electricinduction melting/casting+rolling engineeringroute: zincspecificheat0.388kJ/kgK,latentheat112kJ/kg,reference20-25Cfeedheatedto500C,idealheat0.2963MJ/kg;50% melterefficiency and0.05kWh/kg rollingallowance give0.22590643274853806kWh/kg netfoil. These thermalconstants andselectedefficiency/rollingelectricity are engineeringreferences,not a measured electrodefoilline. Testmelterefficiency30-80%,rolling0.01-0.1kWh/kg andyield90-100%. Do not read EPD cumulativeA1-A3 environmentalenergyindicators as processfuel consumption,which would doublecountrefinedZnproduction. Transfer only its documentedprocessarchitecture and0.08g/kg lubricant coefficient; do not transferbuildingalloyCu/Ti additions,coating,longbuildinglife or moduleDcredits. Genericlubricatingoil is the emulsion-supplyproxy;coolingwater,emulsiondilution,highpuritypowder/foilprocessing,surfacepreparation andfactoryequipmentareunresolved. Manufacturingwaste usesmixedhazardoustreatment proxy without inventedZnrecoverycredit. Legacyfeltprovider remainsavailable but theHFB stackbuys only the newfoilreference at unchangedmass. Metalcharacterization mustfollowrealZn feed,not a copper-shapingservice. No native,runtime,YAML edits or primary-secondaryshare changes.</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18391,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode production, casting and rolling</t>
         </is>
       </c>
       <c r="B991">
@@ -18410,12 +18414,12 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode, casting and rolling</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>zinc foil electrode, casting and rolling engineering reference</t>
+          <t xml:space="preserve">zinc foil electrode, casting and rolling</t>
         </is>
       </c>
     </row>
@@ -18567,7 +18571,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET production, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -18601,7 +18605,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18641,8 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter CSD19536KCS, declared package-material reference. Former reference product: RFB converter CSD19536KCS, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=CSD19536KCS;firstvariant;materialmg={'Aluminum': 2.078818, 'Nickel': 0.000671, 'Silicon': 4e-06, 'Lead': 16.43543, 'Tin': 170.8789, 'Silver': 0.26367, 'Copper': 1367.945, 'Iron': 1.644, 'Phosphorus': 0.411, 'Silica': 395.438103, 'Metal Hydroxide': 42.368368, 'Carbon Black': 2.824558, 'Epoxy': 124.280547, 'Doped Silicon': 19.851772};unknownkg={'Metal Hydroxide': 4.2368368e-05}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
       </c>
@@ -18699,7 +18704,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET production, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1007">
@@ -18722,12 +18727,12 @@
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19234,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver production, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19268,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19304,8 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter UCC27524AQDRQ1, declared package-material reference. Former reference product: RFB converter UCC27524AQDRQ1, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=UCC27524AQDRQ1;firstvariant;materialmg={'Yttrium': 1e-06, 'Gold': 0.161614, 'Silver': 0.183922, 'Epoxy': 6.3863900000000005, 'Copper': 12.8106, 'Iron': 0.3432, 'Phosphorus': 0.0198, 'Zinc': 0.0264, 'Nickel': 0.09512, 'Palladium': 0.0041, 'Phenolic Resin': 2.11347, 'Fused Silica': 51.629055, 'Carbon Black': 0.301924, 'Doped Silicon': 0.75243};unknownkg={}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
       </c>
@@ -19361,7 +19367,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver production, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1033">
@@ -19384,12 +19390,12 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19932,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller production, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19966,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -19996,7 +20002,8 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter TMS320F28035PNT, declared package-material reference. Former reference product: RFB converter TMS320F28035PNT, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=TMS320F28035PNT;firstvariant;materialmg={'Aluminum': 1e-06, 'Copper': 240.17908, 'Iron': 5.783354, 'Proprietary Materials': 4.7e-05, 'Gold': 0.033028, 'Palladium': 0.166628, 'Silver': 2.7728189999999997, 'Epoxy': 42.136409, 'Phosphorus': 0.203033, 'Lead': 0.036915, 'Zinc': 0.307625, 'Nickel': 3.469026, 'Fused Silica': 309.998135, 'Carbon Black': 1.056812, 'Chlorine': 0.003523, 'Doped Silicon': 14.182021};unknownkg={'Proprietary Materials': 4.7e-11}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
       </c>
@@ -20058,7 +20065,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller production, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1060">
@@ -20081,12 +20088,12 @@
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20665,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20699,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -20728,7 +20735,8 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 650V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 650V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 2.6459999999999997e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 5.601e-06, 'carbon': 2.0046e-05, 'epoxy': 0.00038086799999999997, 'silica': 0.0016036569999999999, 'Sn': 3.2692e-05, 'Ni': 2.9065e-05, 'Sb': 1.26e-07, 'Ag': 3.14e-07}</t>
         </is>
       </c>
@@ -20790,7 +20798,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
       <c r="B1088">
@@ -20813,12 +20821,12 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -21285,7 +21293,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -21319,7 +21327,7 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -21355,7 +21363,8 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 1200V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 1200V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 4.941e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 4.257e-06, 'carbon': 2.0032e-05, 'epoxy': 0.000380613, 'silica': 0.00160258, 'Sn': 3.3233e-05, 'Ni': 2.9065e-05, 'Sb': 2.0899999999999998e-07, 'Ag': 5.23e-07}</t>
         </is>
       </c>
@@ -21417,7 +21426,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="B1113">
@@ -21440,12 +21449,12 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -21912,7 +21921,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver production, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21955,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -21982,7 +21991,8 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage isolated gate driver, declared material reference. Former reference product: RFB AC-stage isolated gate driver, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. UCC21710firstMCDvarianthttps://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1;manufacturerledger={'Copper': 309.564275, 'Nickel': 0.168363, 'Proprietary Materials': 1.5e-05, 'Gold': 0.0014520000000000002, 'Palladium': 0.010566, 'Silver': 0.9804740000000001, 'Epoxy': 37.038359, 'Iron': 7.4636, 'Phosphorus': 0.26202, 'Lead': 0.04764, 'Zinc': 0.397, 'Fused Silica': 328.633964, 'Carbon Black': 1.835944, 'Chlorine': 0.007344, 'Doped Silicon': 6.823678}</t>
         </is>
       </c>
@@ -22044,7 +22054,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver production, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1138">
@@ -22067,12 +22077,12 @@
       </c>
       <c r="G1138" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1138" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver, redox-flow battery converter</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22584,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter production, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
     </row>
@@ -22608,7 +22618,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22654,8 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB bidirectional power converter, low-voltage5kW system reference. Former reference product: RFB bidirectional power converter, low-voltage5kW system reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Finishednominalmass=18.491259364830004kg;bulkledger={'Al': 7.64, 'Cu': 3.06, 'steel': 1.45, 'PP': 1.41, 'electrolytic': 0.412, 'film': 0.267, 'ferrite': 2.16, 'PCB': 1.6940000000000002, 'resistors': 0.01, 'diodes': 0.01, 'connectors': 0.01};packagecounts={'CSD19536KCS': 126, 'UCC27524AQDRQ1': 72, 'TMS320F28035PNT': 19, '650V': 6, '1200V': 6, 'ACdriver': 12};nominalpackagemasses={'CSD19536KCS': 0.002144420841, 'UCC27524AQDRQ1': 7.482802600000001e-05, 'TMS320F28035PNT': 0.000620328456, '650V': 0.006047253, '1200V': 0.006047690999999999, 'ACdriver': 0.000693234694}</t>
         </is>
       </c>
@@ -22706,7 +22717,7 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter production, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
       <c r="B1164">
@@ -22729,19 +22740,19 @@
       </c>
       <c r="G1164" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
       <c r="I1164" t="inlineStr">
         <is>
-          <t>RFB bidirectional power converter, low-voltage5kW system reference</t>
+          <t xml:space="preserve">bidirectional power converter, redox-flow battery, low voltage, 5 kW</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET production, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1165">
@@ -22764,19 +22775,19 @@
       </c>
       <c r="G1165" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1165" t="inlineStr">
         <is>
-          <t>RFB converter CSD19536KCS, declared package-material reference</t>
+          <t xml:space="preserve">MOSFET, CSD19536KCS, redox-flow battery converter</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver production, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1166">
@@ -22799,19 +22810,19 @@
       </c>
       <c r="G1166" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1166" t="inlineStr">
         <is>
-          <t>RFB converter UCC27524AQDRQ1, declared package-material reference</t>
+          <t xml:space="preserve">gate driver, UCC27524AQDRQ1, redox-flow battery converter</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller production, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1167">
@@ -22834,19 +22845,19 @@
       </c>
       <c r="G1167" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1167" t="inlineStr">
         <is>
-          <t>RFB converter TMS320F28035PNT, declared package-material reference</t>
+          <t xml:space="preserve">microcontroller, TMS320F28035PNT, redox-flow battery converter</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
       <c r="B1168">
@@ -22869,19 +22880,19 @@
       </c>
       <c r="G1168" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
       <c r="I1168" t="inlineStr">
         <is>
-          <t>RFB AC-stage 650V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="B1169">
@@ -22904,19 +22915,19 @@
       </c>
       <c r="G1169" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="I1169" t="inlineStr">
         <is>
-          <t>RFB AC-stage 1200V SiC switch, TO247 material reference</t>
+          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver production, redox-flow battery converter</t>
         </is>
       </c>
       <c r="B1170">
@@ -22939,12 +22950,12 @@
       </c>
       <c r="G1170" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver, redox-flow battery converter</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
         <is>
-          <t>RFB AC-stage isolated gate driver, declared material reference</t>
+          <t xml:space="preserve">isolated gate driver, redox-flow battery converter</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="B381">
-        <v>1</v>
+        <v>0.0024878048780487805</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
         </is>
       </c>
     </row>
@@ -17739,7 +17739,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
         </is>
       </c>
     </row>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,8 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Former reference product: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished 10%-Pd/C catalyst supplied and ultimately retired. Unit field: kilogram. Former reference: 1 unit = 0.0024878048780487805 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Former reference product: Pd-C catalyst lifetime consumption, TEMPTMA source-batch reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.</t>
         </is>
       </c>
@@ -17850,7 +17851,7 @@
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
@@ -17860,12 +17861,12 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA</t>
+          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17877,7 @@
         </is>
       </c>
       <c r="B962">
-        <v>0.0024878048780487805</v>
+        <v>1.0</v>
       </c>
       <c r="C962" t="inlineStr">
         <is>
@@ -17911,7 +17912,7 @@
         </is>
       </c>
       <c r="B963">
-        <v>-0.0024878048780487805</v>
+        <v>-1.0</v>
       </c>
       <c r="C963" t="inlineStr">
         <is>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -18642,7 +18642,9 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter CSD19536KCS, declared package-material reference. Former reference product: RFB converter CSD19536KCS, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB converter CSD19536KCS, declared package-material reference. Former reference product: RFB converter CSD19536KCS, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=CSD19536KCS;firstvariant;materialmg={'Aluminum': 2.078818, 'Nickel': 0.000671, 'Silicon': 4e-06, 'Lead': 16.43543, 'Tin': 170.8789, 'Silver': 0.26367, 'Copper': 1367.945, 'Iron': 1.644, 'Phosphorus': 0.411, 'Silica': 395.438103, 'Metal Hydroxide': 42.368368, 'Carbon Black': 2.824558, 'Epoxy': 124.280547, 'Doped Silicon': 19.851772};unknownkg={'Metal Hydroxide': 4.2368368e-05}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
@@ -19160,11 +19162,11 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>market for silicon, electronics grade</t>
+          <t>market for wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
       <c r="B1020">
-        <v>1.9851772000000002e-05</v>
+        <v>3.155582896200922e-05</v>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
@@ -19173,7 +19175,7 @@
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
@@ -19183,12 +19185,17 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes. This part: die silicon 1.9851772e-05 kg; fabricated output 3.1555828962e-05 m2 per part.</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>
@@ -19305,7 +19312,9 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter UCC27524AQDRQ1, declared package-material reference. Former reference product: RFB converter UCC27524AQDRQ1, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB converter UCC27524AQDRQ1, declared package-material reference. Former reference product: RFB converter UCC27524AQDRQ1, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=UCC27524AQDRQ1;firstvariant;materialmg={'Yttrium': 1e-06, 'Gold': 0.161614, 'Silver': 0.183922, 'Epoxy': 6.3863900000000005, 'Copper': 12.8106, 'Iron': 0.3432, 'Phosphorus': 0.0198, 'Zinc': 0.0264, 'Nickel': 0.09512, 'Palladium': 0.0041, 'Phenolic Resin': 2.11347, 'Fused Silica': 51.629055, 'Carbon Black': 0.301924, 'Doped Silicon': 0.75243};unknownkg={}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
@@ -19858,11 +19867,11 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>market for silicon, electronics grade</t>
+          <t>market for wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
       <c r="B1047">
-        <v>7.524300000000001e-07</v>
+        <v>1.1960419647114925e-06</v>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
@@ -19871,7 +19880,7 @@
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
@@ -19881,12 +19890,17 @@
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes. This part: die silicon 7.5243e-07 kg; fabricated output 1.19604196471e-06 m2 per part.</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>
@@ -20003,7 +20017,9 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB converter TMS320F28035PNT, declared package-material reference. Former reference product: RFB converter TMS320F28035PNT, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB converter TMS320F28035PNT, declared package-material reference. Former reference product: RFB converter TMS320F28035PNT, declared package-material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. Manufacturer materialreport https://www.ti.com/quality-reliability-packaging-download/en-us/report?opn=TMS320F28035PNT;firstvariant;materialmg={'Aluminum': 1e-06, 'Copper': 240.17908, 'Iron': 5.783354, 'Proprietary Materials': 4.7e-05, 'Gold': 0.033028, 'Palladium': 0.166628, 'Silver': 2.7728189999999997, 'Epoxy': 42.136409, 'Phosphorus': 0.203033, 'Lead': 0.036915, 'Zinc': 0.307625, 'Nickel': 3.469026, 'Fused Silica': 309.998135, 'Carbon Black': 1.056812, 'Chlorine': 0.003523, 'Doped Silicon': 14.182021};unknownkg={'Proprietary Materials': 4.7e-11}. Ytrace representedbycontainedYequivalentY2O3feedproxy,notmetalwiremanufacturingrecipe.</t>
         </is>
@@ -20591,11 +20607,11 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>market for silicon, electronics grade</t>
+          <t>market for wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
       <c r="B1075">
-        <v>1.4182021e-05</v>
+        <v>2.2543349229057383e-05</v>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
@@ -20604,7 +20620,7 @@
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
@@ -20614,12 +20630,17 @@
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes. This part: die silicon 1.4182021e-05 kg; fabricated output 2.25433492291e-05 m2 per part.</t>
         </is>
       </c>
       <c r="I1075" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>
@@ -21992,7 +22013,9 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage isolated gate driver, declared material reference. Former reference product: RFB AC-stage isolated gate driver, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage isolated gate driver, declared material reference. Former reference product: RFB AC-stage isolated gate driver, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. UCC21710firstMCDvarianthttps://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1;manufacturerledger={'Copper': 309.564275, 'Nickel': 0.168363, 'Proprietary Materials': 1.5e-05, 'Gold': 0.0014520000000000002, 'Palladium': 0.010566, 'Silver': 0.9804740000000001, 'Epoxy': 37.038359, 'Iron': 7.4636, 'Phosphorus': 0.26202, 'Lead': 0.04764, 'Zinc': 0.397, 'Fused Silica': 328.633964, 'Carbon Black': 1.835944, 'Chlorine': 0.007344, 'Doped Silicon': 6.823678}</t>
         </is>
@@ -22545,11 +22568,11 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>market for silicon, electronics grade</t>
+          <t>market for wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
       <c r="B1152">
-        <v>6.823678e-06</v>
+        <v>1.0846730249562868e-05</v>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
@@ -22558,7 +22581,7 @@
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
@@ -22568,12 +22591,17 @@
       </c>
       <c r="G1152" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>SILICON DIE FABRICATION COVERAGE CORRECTION, 2026-10-19. TI material-content declarations, first assembly variant only: https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=CSD19536KCS ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC27524AQDRQ1 ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=TMS320F28035PNT ; https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=UCC21710QDWRQ1 . Replace only the identified DOPED SILICON die feed by native fabricated-wafer supply; raw electronic-grade silicon alone did not buy FEOL/BEOL lithography, doping, process gases, cleanroom utilities or wafer-fabrication waste treatment. The native wafer supplier includes those operations and its own wafer-yield burden (1.8182 m2 raw wafer per m2 fabricated output in ecoinvent 3.12); do not apply a second fabrication-yield multiplier. Area = declared die silicon kg / (2330 kg/m3 * 0.000270 m). The 270 micrometre reference matches the native single-Si electronic-wafer documentation (about 0.629 kg/m2). It is a consistent source geometry, NOT a measured thickness or fab node for this TI part. Die thinning/technology remain sensitivity parameters: illustrative 100/270/400 micrometre comparisons are reported separately, not a measured uncertainty distribution. Use a generic historical silicon IC fabrication process proxy for these silicon devices; actual power-MOSFET/control-IC recipes differ. Preserve all retained package-metal, filler, resin and assembly inputs, part counts, functional output, whole-converter EOL and lifetime. No complete packaged IC is purchased on top of the material ledger. The MOSFET trace silicon impurity (4e-12 kg/part) remains raw silicon; only its 19.851772 mg die is replaced. SiC switches are excluded: silicon wafer fabrication is not a demonstrated SiC substrate, epitaxy and device-manufacturing route. Packaging process energy, power-device geometry and unreported fractions remain evidence gaps, not claimed validated by this correction. Existing supplemental workbook only; no native, runtime, market-share or metal-factor changes. This part: die silicon 6.823678e-06 kg; fabricated output 1.08467302496e-05 m2 per part.</t>
         </is>
       </c>
       <c r="I1152" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -20757,7 +20757,9 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 650V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 650V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 650V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 650V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 2.6459999999999997e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 5.601e-06, 'carbon': 2.0046e-05, 'epoxy': 0.00038086799999999997, 'silica': 0.0016036569999999999, 'Sn': 3.2692e-05, 'Ni': 2.9065e-05, 'Sb': 1.26e-07, 'Ag': 3.14e-07}</t>
         </is>
@@ -20855,7 +20857,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>market for silicon carbide</t>
+          <t>silicon carbide wafer production, physical vapour transport</t>
         </is>
       </c>
       <c r="B1089">
@@ -20878,12 +20880,17 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21392,9 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 1200V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 1200V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 1200V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 1200V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
  BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 4.941e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 4.257e-06, 'carbon': 2.0032e-05, 'epoxy': 0.000380613, 'silica': 0.00160258, 'Sn': 3.3233e-05, 'Ni': 2.9065e-05, 'Sb': 2.0899999999999998e-07, 'Ag': 5.23e-07}</t>
         </is>
@@ -21483,7 +21492,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>market for silicon carbide</t>
+          <t>silicon carbide wafer production, physical vapour transport</t>
         </is>
       </c>
       <c r="B1114">
@@ -21506,12 +21515,17 @@
       </c>
       <c r="G1114" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
       <c r="I1114" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1192"/>
+  <dimension ref="A1:N1218"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -7767,422 +7767,644 @@
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A359" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B359" s="1" t="s">
-        <v>514</v>
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G359" s="8"/>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A360" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>7</v>
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B360" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A361" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>515</v>
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B361" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A362" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>10</v>
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A363" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>19</v>
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A364" s="1" t="s">
-        <v>43</v>
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>APPROVED TEMPTMA Pd/C COVERAGE, issue80,2026-10-18. Jenabatteries EP3497081A1,priority2016,Example1:98.4gTAA,3.6gPd/C at10wt%Pd,110.9gcrudeintermediate. https://patents.google.com/patent/EP3497081A1/en . Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Original intermediate1description explicitly uses filtered/reusedPd/C but has no catalyst input. Scale the patent finished-catalyst charge3.6g per98.4gTAA to existing0.68kgTAA batch: 0.024878048780487806kg catalyst inventory; retain original batch output0.764304412864622kg and all other reaction ingredients/utilities. Adopt10 productive batch uses per initial catalyst charge as an explicit ILLUSTRATIVE engineering lifetime, not measured catalyst durability. Allocate charge/10 fresh catalyst and equal retired mixed catalyst waste per source batch inside oneunit lifetime-consumption helper. Parent buys oneunit; do not divide again by productmass or buy the fullcharge everybatch. Sensitivity1,10,100uses changes only catalyst fresh/retired dose, giving a100fold range; no empirical probability/confidenceinterval is claimed. The patent establishes charge/composition, not reuse life; a zeroPd result from infinitely reused stock is not justified. Finishedcatalyst dryreference10wt%Pd+90wt%activatedcarbon; source carrier moisture/dispersion are unspecified, so generic granular carbon is a support-supply proxy rather than a validated commercial powderedcatalyst. Manufacturingretention95% and1kWh/kg catalyst deposition/conditioning are explicit assumptions with90-100%retention sensitivity; match manufacturingloss waste, no extra fullPGMrefining inventory in parallel with the Pd market. Retired catalyst uses the existing mixed hazardous-incineration proxy with no invented palladium recovery/substitution credit; actual catalyst regeneration/recovery and loss routing remain unresolved. This is not a primary-secondaryshare analysis. Batch manufacture is not annual vehicle procurement. Sourcepatent crudeproduct110.9g is distinct from the inherited modeled batchyield; retain the accepted source-batchTAA denominator so this correction supplies missingcatalyst rather than silently reconstructing allTEMPTMA chemistry. Actual industrialcyclelife is a material uncertainty in systemPd,not evidence the illustrative reference is the correct measured quantity. No native,runtime orYAML edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-TEMPTMA was modeled based on the production process described by "Worldwide Pat., 2016". First, TAA is reacted with dimethylamine under palladium-C catalyst at -10°C. Hydrogen is then added to the reaction mixture at 60°C. Afterwards, the catalyst is filtered and reused in the same process. The solvent was recirculated as well. In this step, Intermediate 1 is produced. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛. 
-Intermediate 1 obtained in the previous step is dissolved in a 1:1 mixture of acetonitrile and toluene and transferred to a pressure reactor. After that, the reaction mixture is heated to 70°C, and chloromethane is added. Then, the precipitation is collected by reducing the temperature to 20°C. The precipitation is then washed with toluene, to obtain Intermediate 2. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛. 
-The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A365" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B365" s="1" t="s">
-        <v>468</v>
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B365" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A366" s="1" t="s">
-        <v>12</v>
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A367" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F367" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G367" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H367" s="2" t="s">
-        <v>8</v>
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B367" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C367" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D367" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E367" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G367" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A368" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B368" s="1">
-        <v>1.1256317531962401</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F368" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G368" s="1" t="s">
-        <v>252</v>
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G368" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A369" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="B369" s="1">
-        <v>0.76430441286462203</v>
-      </c>
-      <c r="C369" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F369" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G369" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H369" s="1" t="s">
-        <v>515</v>
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H369" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A370" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="B370" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="C370" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G370" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H370" s="1" t="s">
-        <v>491</v>
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H370" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A371" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B371" s="1">
-        <v>2.4233664287107901E-3</v>
-      </c>
-      <c r="C371" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D371" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F371" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G371" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H371" s="1" t="s">
-        <v>258</v>
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G371" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H371" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A372" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B372" s="1">
-        <v>3.87738628593726E-2</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D372" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G372" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H372" s="1" t="s">
-        <v>256</v>
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G372" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H372" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A373" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B373" s="1">
-        <v>0.39489999999999997</v>
-      </c>
-      <c r="C373" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D373" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F373" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G373" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H373" s="1" t="s">
-        <v>292</v>
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G373" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H373" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A374" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B374" s="1">
-        <v>0.824825813516879</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F374" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G374" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H374" s="1" t="s">
-        <v>260</v>
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G374" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H374" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A375" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B375" s="1">
-        <v>0.13747096891947999</v>
-      </c>
-      <c r="C375" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D375" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F375" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G375" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H375" s="1" t="s">
-        <v>268</v>
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G375" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H375" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A376" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B376" s="1">
-        <v>0.27412074543889497</v>
-      </c>
-      <c r="C376" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F376" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G376" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H376" s="1" t="s">
-        <v>256</v>
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G376" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H376" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A377" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B377" s="1">
-        <v>0.37481400764060202</v>
-      </c>
-      <c r="C377" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G377" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H377" s="1" t="s">
-        <v>291</v>
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G377" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H377" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A378" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B378" s="1">
-        <v>1.8094469334373899</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G378" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H378" s="1" t="s">
-        <v>257</v>
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G378" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H378" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A379" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B379" s="1">
-        <v>-0.31059999999999999</v>
-      </c>
-      <c r="C379" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D379" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G379" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H379" s="1" t="s">
-        <v>269</v>
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G379" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H379" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A380" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B380" s="1">
-        <v>-0.37481400764060202</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D380" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F380" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G380" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H380" s="1" t="s">
-        <v>261</v>
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G380" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H380" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst supply and spent catalyst treatment, for TEMPTMA production</t>
-        </is>
-      </c>
-      <c r="B381">
-        <v>0.0024878048780487805</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t xml:space="preserve">kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -23772,6 +23994,651 @@
         </is>
       </c>
     </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>4-dimethylamino-2,2,6,6-tetramethylpiperidine production, intermediate 1, for RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>4-dimethylamino-2,2,6,6-tetramethylpiperidine, intermediate 1, for RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>SOURCE-VERSION SUPPLIER COMPATIBILITY, 2026-10-20. Use the existing hydrogen market in the workbook ecoinvent 3.9 vocabulary: market for hydrogen, liquid / hydrogen, liquid / RER / kilogram. The official 3.9-to-3.10 migration maps this legacy identity to market for hydrogen, gaseous, medium pressure, merchant. It is the same background identity used by the other RFB hydrogenation, not an added liquefaction service. Retain the newly restored net-reactant amount; all other exchanges and functional output stay unchanged. The net stoichiometric minimum and unquantified losses/catalyst/process limitations below remain in force.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+NET HYDROGEN REACTANT CORRECTION, 2026-10-20. https://patents.google.com/patent/EP3497081A1/en , Example 1 first synthesis step, ketone conversion under hydrogen at 60 C up to 3 bar. Source LCA: Zhang et al. 2025, https://doi.org/10.1039/D4EB00027G . Balanced reaction: C9H17NO + C2H7N + H2 -&gt; C11H24N2 + H2O. One mole of molecular H2 is consumed per mole of ketone, not half a mole. TAA molar mass = 155.241000 g/mol; H2 = 2.016000 g/mol. The existing 0.68 kg TAA feed therefore requires 0.00883065684967245 kg net H2 per declared source batch under the retained full-ketone-conversion reference. This includes conversion of material subsequently lost during isolation: do not apply the isolated-product yield a second time. Use the existing RER merchant medium-pressure gaseous-hydrogen market, already used by the other RFB hydrogenation. Nitrogen is an inert-gas input and is preserved; air separation cannot supply reacting hydrogen. Recirculation can return EXCESS H2, but cannot return H2 atoms incorporated into product or reaction water. This net stoichiometric amount is an explicit minimum-consumption reference, not measured fresh plant gas. Additional purge/vent losses, side reactions, recycle compression and gross circulating flow are unquantified. No zero-loss industrial claim, new operating-energy allowance or fabricated vent/waste composition is introduced. Preserve existing batch product output, other reagents, utilities, freight, existing waste services, catalyst and battery sizing. The wider process inventory is not certified as mass-balanced by this single-reactant correction. Existing supplemental workbook only; no native inventory, runtime, YAML or indicator-definition changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Heat, waste</t>
+        </is>
+      </c>
+      <c r="B1204">
+        <v>1.12563175319624</v>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>4-dimethylamino-2,2,6,6-tetramethylpiperidine production, intermediate 1, for RFB</t>
+        </is>
+      </c>
+      <c r="B1205">
+        <v>0.764304412864622</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>4-dimethylamino-2,2,6,6-tetramethylpiperidine, intermediate 1, for RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>triacetonamine production</t>
+        </is>
+      </c>
+      <c r="B1206">
+        <v>0.68</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>triacetonamine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>air separation, cryogenic</t>
+        </is>
+      </c>
+      <c r="B1207">
+        <v>0.00242336642871079</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>electricity production, medium voltage, petroleum refinery operation</t>
+        </is>
+      </c>
+      <c r="B1208">
+        <v>0.0387738628593726</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>market for dimethylamine</t>
+        </is>
+      </c>
+      <c r="B1209">
+        <v>0.3949</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>dimethylamine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1210">
+        <v>0.824825813516879</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B1211">
+        <v>0.13747096891948</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1212">
+        <v>0.274120745438895</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>methanol production</t>
+        </is>
+      </c>
+      <c r="B1213">
+        <v>0.374814007640602</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>methanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>steam production, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B1214">
+        <v>1.80944693343739</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, hazardous waste incineration, with energy recovery</t>
+        </is>
+      </c>
+      <c r="B1215">
+        <v>-0.3106</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>treatment of spent solvent mixture, hazardous waste incineration, with energy recovery</t>
+        </is>
+      </c>
+      <c r="B1216">
+        <v>-0.374814007640602</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>palladium catalyst supply and spent catalyst treatment, for TEMPTMA production</t>
+        </is>
+      </c>
+      <c r="B1217">
+        <v>0.0024878048780487805</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>palladium catalyst, 10% palladium on activated carbon, including spent catalyst treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>market for hydrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1218">
+        <v>0.008830656849672446</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>hydrogen, liquid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2792,8 +2792,13 @@
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>519</v>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>NET HYDROGEN REACTANT CORRECTION, 2026-10-20. https://patents.google.com/patent/CN115010650A/en , Example 1 and process description, carbonyl hydrogenation with excess-H2 recirculation. Source LCA: Zhang et al. 2025, https://doi.org/10.1039/D4EB00027G . Balanced reaction: C9H17NO + H2 -&gt; C9H19NO. One mole of molecular H2 is consumed per mole of ketone, not half a mole. TAA molar mass = 155.241000 g/mol; H2 = 2.016000 g/mol. The existing 0.155241 kg TAA feed therefore requires 0.002016 kg net H2 per declared source batch under the retained full-ketone-conversion reference. This includes conversion of material subsequently lost during isolation: do not apply the isolated-product yield a second time. Use the same RER hydrogen market as the other RFB hydrogenation. In this workbook source-version vocabulary it is named market for hydrogen, liquid; the standard ecoinvent 3.9-to-3.10 migration maps that legacy label to market for hydrogen, gaseous, medium pressure, merchant. This is not an extra hydrogen-liquefaction service. Nitrogen is an inert-gas input and is preserved; air separation cannot supply reacting hydrogen. Recirculation can return EXCESS H2, but cannot return H2 atoms incorporated into product or reaction water. This net stoichiometric amount is an explicit minimum-consumption reference, not measured fresh plant gas. Additional purge/vent losses, side reactions, recycle compression and gross circulating flow are unquantified. No zero-loss industrial claim, new operating-energy allowance or fabricated vent/waste composition is introduced. Preserve existing batch product output, other reagents, utilities, freight, existing waste services, catalyst and battery sizing. The wider process inventory is not certified as mass-balanced by this single-reactant correction. Existing supplemental workbook only; no native inventory, runtime, YAML or indicator-definition changes. The inherited note claimed a 1:0.5 TAA:H2 stoichiometric ratio; that half-equivalent is incorrect for reduction of a ketone to an alcohol. The patent stated circulating 1:1.5 ratio and its example mass flows are not mutually consistent; neither is treated as a measured fresh-gas dose. The selected correction uses the unambiguous one-equivalent chemical requirement. The source Ni/Al2O3 catalyst and its preparation are also missing from this inherited inventory; their dose, nickel fraction and throughput must be reconstructed separately, not silently assumed zero.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+4-OH-TEMP is modeled based on the production process described by "China Pat., CN115010650A, 2022". 15 wt% of triacetone amine in isoprophyl alcohol solvent is mixed with hydrogen in gas-liquid mixer at 110℃, the molar ratio of triacetone amine to hydrogen is 1:1.5. However, since excess hydrogen is recycled and reused for the same process, it is assumed that the molar ratio of triacetone amine to hydrogen rather follows the stoichiometric ratio (1:0.5) per unit of production. The reaction time per unit is assumed to be 3h. The LCI for ethylenediaminetetraacetic acid (EDTA) disodium salt was estimated by the reaction of EDTA with two portions of NaOH in suitable pH.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -2946,7 +2951,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="1">
-        <v>1E-3</v>
+        <v>0.002016</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -4704,8 +4704,16 @@
       <c r="A144" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>523</v>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>TEMPTMA OXIDATION REAGENT-BASIS CORRECTION, 2026-10-20. Source: https://patents.google.com/patent/EP3497081A1/en , Example 1, step B. Its batch contains 90 g intermediate 2, 3 g NaOH (75 mmol), 2.3 g anhydrous MgSO4, 120 mL water and 1.15 mol H2O2 (117 mL of 30 wt% solution); reported recovered product is 96 g. The current reference output is 1 kg product and already buys 90/96 = 0.9375 kg intermediate 2. Normalize the corrected reagent to the SAME 96 g product, not 90 g reactant or a litre of solution. The native without-water reference products count pure chemical mass. The concentration in their names describes delivery state, not a second multiplier on an already-pure dose. This is a patent-route reference, not a measured industrial vendor process. Other uncorrected process, pH-adjustment, utility, isolation/purity and waste inventories are not certified by this targeted reagent correction. Existing supplemental workbook only; no native, runtime, YAML or indicator edits. Restore 0.003/0.096 = 0.03125 kg PURE NaOH/kg product, replacing 0.0000939 kg/kg. The original 3 g and 75 mmol specify neat NaOH equivalent; do not divide by two for the 50% market. Retain the existing GLO market and its standard regional migration shares. Do not change the source product, existing solvent/water estimate, MgSO4, peroxide, catalyst, freight, electricity or wastes in this commit. Aqueous carrier water and full liquid-waste composition remain part of the unresolved process-water balance; no false closed mass balance or fabricated NaOH recovery credit is claimed.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TEMPTMA was modeled based on the production process described by "Worldwide Pat., 2016". First, TAA is reacted with dimethylamine under palladium-C catalyst at -10°C. Hydrogen is then added to the reaction mixture at 60°C. Afterwards, the catalyst is filtered and reused in the same process. The solvent was recirculated as well. In this step, Intermediate 1 is produced. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛.
+Intermediate 1 obtained in the previous step is dissolved in a 1:1 mixture of acetonitrile and toluene and transferred to a pressure reactor. After that, the reaction mixture is heated to 70°C, and chloromethane is added. Then, the precipitation is collected by reducing the temperature to 20°C. The precipitation is
+then washed with toluene, to obtain Intermediate 2. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛.
+Subsequently, Intermediate 2, sodium hydroxide, and magnesium sulfate (MgSO4) are dissolved in water. The mixture is then heated to 90°C, and 30wt% hydrogen peroxide (H2O2) is added dropwise. Afterwards, it takes a few days for the chemical mixture to react. Here, an approximate reaction time (24 h) is applied in the calculations. When the reaction is finished, the resulting precipitate (exhausted MgSO4) is removed by filtration, and the pH of the solution is adjusted to 5. The solution is then stirred at 90°C to remove hydrogen peroxide. The desired product TEMPTMA is obtained after removing water and drying at 40°C. The process was scaled up in LCA model, meaning that solvent usage was reduced by 20%, and solvent recirculation was considered, following the approach described above in the production of TEMPO-4-sulfate potassium.
+The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+        </is>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4795,7 +4803,7 @@
         <v>50</v>
       </c>
       <c r="B150" s="4">
-        <v>9.3900000000000006E-5</v>
+        <v>0.03125</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>38</v>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -4706,7 +4706,9 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>TEMPTMA OXIDATION REAGENT-BASIS CORRECTION, 2026-10-20. Source: https://patents.google.com/patent/EP3497081A1/en , Example 1, step B. Its batch contains 90 g intermediate 2, 3 g NaOH (75 mmol), 2.3 g anhydrous MgSO4, 120 mL water and 1.15 mol H2O2 (117 mL of 30 wt% solution); reported recovered product is 96 g. The current reference output is 1 kg product and already buys 90/96 = 0.9375 kg intermediate 2. Normalize the corrected reagent to the SAME 96 g product, not 90 g reactant or a litre of solution. The native without-water reference products count pure chemical mass. The concentration in their names describes delivery state, not a second multiplier on an already-pure dose. This is a patent-route reference, not a measured industrial vendor process. Other uncorrected process, pH-adjustment, utility, isolation/purity and waste inventories are not certified by this targeted reagent correction. Existing supplemental workbook only; no native, runtime, YAML or indicator edits. Restore 0.003/0.096 = 0.03125 kg PURE NaOH/kg product, replacing 0.0000939 kg/kg. The original 3 g and 75 mmol specify neat NaOH equivalent; do not divide by two for the 50% market. Retain the existing GLO market and its standard regional migration shares. Do not change the source product, existing solvent/water estimate, MgSO4, peroxide, catalyst, freight, electricity or wastes in this commit. Aqueous carrier water and full liquid-waste composition remain part of the unresolved process-water balance; no false closed mass balance or fabricated NaOH recovery credit is claimed.
+          <t>TEMPTMA OXIDATION REAGENT-BASIS CORRECTION, 2026-10-20. Source: https://patents.google.com/patent/EP3497081A1/en , Example 1, step B. Its batch contains 90 g intermediate 2, 3 g NaOH (75 mmol), 2.3 g anhydrous MgSO4, 120 mL water and 1.15 mol H2O2 (117 mL of 30 wt% solution); reported recovered product is 96 g. The current reference output is 1 kg product and already buys 90/96 = 0.9375 kg intermediate 2. Normalize the corrected reagent to the SAME 96 g product, not 90 g reactant or a litre of solution. The native without-water reference products count pure chemical mass. The concentration in their names describes delivery state, not a second multiplier on an already-pure dose. This is a patent-route reference, not a measured industrial vendor process. Other uncorrected process, pH-adjustment, utility, isolation/purity and waste inventories are not certified by this targeted reagent correction. Existing supplemental workbook only; no native, runtime, YAML or indicator edits. Restore 1.15 mol * 34.014000 g/mol / 96 g product = 0.407459375 kg PURE H2O2/kg product, replacing 0.1184 kg/kg. Use the explicitly stated moles, rather than inventing a density from rounded solution volume. The purchased 50 wt% stock carries one kg water per kg pure peroxide; add only the dilution deficit H2O2*(1/0.30-1/0.50) = 0.543279166666667 kg deionised water/kg product to represent the source 30 wt% addition. Do not buy the full 30% solution mass as pure H2O2, or add its full carrier water again. This dilution water is additional to the inherited initial makeup-water estimate; that estimate and the existing solvent scaling are retained, not independently revalidated. Peroxide decomposition, pH-adjustment reagents, condensate/recycle and liquid-waste composition remain unresolved; no guessed oxygen vent or extra generic waste treatment is introduced. Preserve the corrected NaOH dose and every other chemical, metal, energy, freight, product-output and battery-service coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+TEMPTMA OXIDATION REAGENT-BASIS CORRECTION, 2026-10-20. Source: https://patents.google.com/patent/EP3497081A1/en , Example 1, step B. Its batch contains 90 g intermediate 2, 3 g NaOH (75 mmol), 2.3 g anhydrous MgSO4, 120 mL water and 1.15 mol H2O2 (117 mL of 30 wt% solution); reported recovered product is 96 g. The current reference output is 1 kg product and already buys 90/96 = 0.9375 kg intermediate 2. Normalize the corrected reagent to the SAME 96 g product, not 90 g reactant or a litre of solution. The native without-water reference products count pure chemical mass. The concentration in their names describes delivery state, not a second multiplier on an already-pure dose. This is a patent-route reference, not a measured industrial vendor process. Other uncorrected process, pH-adjustment, utility, isolation/purity and waste inventories are not certified by this targeted reagent correction. Existing supplemental workbook only; no native, runtime, YAML or indicator edits. Restore 0.003/0.096 = 0.03125 kg PURE NaOH/kg product, replacing 0.0000939 kg/kg. The original 3 g and 75 mmol specify neat NaOH equivalent; do not divide by two for the 50% market. Retain the existing GLO market and its standard regional migration shares. Do not change the source product, existing solvent/water estimate, MgSO4, peroxide, catalyst, freight, electricity or wastes in this commit. Aqueous carrier water and full liquid-waste composition remain part of the unresolved process-water balance; no false closed mass balance or fabricated NaOH recovery credit is claimed.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 TEMPTMA was modeled based on the production process described by "Worldwide Pat., 2016". First, TAA is reacted with dimethylamine under palladium-C catalyst at -10°C. Hydrogen is then added to the reaction mixture at 60°C. Afterwards, the catalyst is filtered and reused in the same process. The solvent was recirculated as well. In this step, Intermediate 1 is produced. The energy required in this step only includes energy needed to reach the reaction temperature 𝐸𝑟𝑒𝑎𝑐𝑡𝑖𝑜𝑛.
 Intermediate 1 obtained in the previous step is dissolved in a 1:1 mixture of acetonitrile and toluene and transferred to a pressure reactor. After that, the reaction mixture is heated to 70°C, and chloromethane is added. Then, the precipitation is collected by reducing the temperature to 20°C. The precipitation is
@@ -4826,7 +4828,7 @@
         <v>65</v>
       </c>
       <c r="B151" s="1">
-        <v>0.11840000000000001</v>
+        <v>0.407459375</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>7</v>
@@ -4941,7 +4943,7 @@
         <v>67</v>
       </c>
       <c r="B156" s="1">
-        <v>1.0026999999999999</v>
+        <v>1.5459791666666667</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>36</v>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1218"/>
+  <dimension ref="A1:N1252"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -4212,452 +4212,718 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>487</v>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>7</v>
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>488</v>
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>10</v>
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>19</v>
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>522</v>
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>468</v>
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>12</v>
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>8</v>
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B122" s="1">
-        <v>2.8462000000000001E-2</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>252</v>
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B123" s="1">
-        <v>2.8449961999999998E-4</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>252</v>
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B124" s="1">
-        <v>0.1751844941</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>488</v>
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="B125" s="1">
-        <v>0.1131003701</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>37</v>
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B126" s="1">
-        <v>3.8102999999999998E-4</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>258</v>
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B127" s="1">
-        <v>0.10160700659999999</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>280</v>
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B128" s="1">
-        <v>0.10160700659999999</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>279</v>
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B129" s="1">
-        <v>6.4399999999999999E-2</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>273</v>
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B130" s="1">
-        <v>0.16356841</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>260</v>
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B131" s="1">
-        <v>2.7261400000000002E-2</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>268</v>
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B132" s="1">
-        <v>1.8096059219999999E-3</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>256</v>
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B133" s="1">
-        <v>6.0964203960000001E-3</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>256</v>
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B134" s="1">
-        <v>6.5736865180000006E-2</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>240</v>
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B135" s="1">
-        <v>0.28449962000000001</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>257</v>
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B136" s="1">
-        <v>-2.7126675439999998E-4</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>261</v>
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B137" s="1">
-        <v>0</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>264</v>
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -24654,6 +24920,899 @@
         </is>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>TEMPO-4-sulfate potassium production, for RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>TEMPO-4-sulfate potassium, electroactive material, RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOURCE-CONSISTENT HYBRID CATHOLYTE SULFATION AND SEPARATION REFERENCE, 2026-10-20. Winsberg et al. 2017 DOI10.1021/acsenergylett.6b00655, SI Experimental Section p1, https://acs.figshare.com/ndownloader/files/7415704 : 5 g TEMPOL, 35 mL concentrated H2SO4 (&gt;95%), 145.31 g KHCO3 in 1.1 L water, two 250 mL ethyl-acetate extractions, 150 mL acetone, 7.83 g recovered product (93%). Rebuild ALL coefficients on this product basis; retain the existing 0.1751844941 kg reference output by multiplying each source batch by 22.3734986079183. The previous almost one-equivalent acid/base recipe did not represent the published excess-acid neutralization; no acid-recovery process was documented to justify it. This is a published-route reference, not a measured industrial plant, nor a new fleet or battery-capacity specification. PARAMETERS: 96wt% acid at 1.84kg/L, an explicitly selected assay within the supplier range, not the original lot assay; VWR95-97% https://www.vwr.com/uk/en/product/782725/sulphuric-acid-95-97-gpr-rectapur . Ethyl acetate .902kg/L, acetone .791kg/L; water1kg/L. Purchase pure H2SO4 mass and its stock water separately. Preserve the existing 20% organic-solvent reduction and 71% recycle as PROSPECTIVE ASSUMPTIONS, not reported experimental recovery; do not apply either reduction to acid, bicarbonate or the initial aqueous solution. At steady state purchase 29% fresh organic solvent and dispose exactly that net solvent mass once, rather than counting internal recycled solvent as another purchase. CHEMISTRY: full TEMPOL conversion with the measured isolated yield; the unrecovered product is allocated to solid process residue, an explicit partition assumption. Acid moles A and TEMPOL moles T require 2A-T bicarbonate moles, producing 2A-T CO2 moles, A-T K2SO4 moles and 2A water moles. Excess bicarbonate remains in the solid residue in the reference; its thermal decomposition is a separate sensitivity. Do not emit every purchased bicarbonate molecule as CO2. Separate noncombustible sulfate/bicarbonate/carbonate salts from the small unrecovered organic product. Route salts to the existing RER underground-deposit waste market as an explicit containment PROXY and organic product loss to mixed chemical-waste incineration. Do not apply an organic-waste combustion carbon profile to all the inorganic salts. Actual treatment and legal hazard classification are unreported; no sale/recovery/substitution credit. Generic treatment emissions are not an assay of this residue. The chosen direct CO2 flow is fossil technical carbon: native carbonate/CO2 suppliers use captured industrial waste gas. Its fossil share is a reference assumption, not a measured provenance split; test zero-to-full fossil characterization separately. No atmospheric-capture credit. SEPARATION: retain the documented empirical 1.4kg steam, .03kWh, .0015Nm3 N2 and .027m3 cooling water per kg RECOVERED organic solvent. N2 density1.25kg/Nm3. Model once-through cooling with tap-water supply and equal noncontact water return; nitrogen input has equal air release. Newly include aqueous evaporation: 20-&gt;60C, cp4.18kJ/kg/K plus latent2357.65kJ/kg (NIST heat-of-vaporization study, https://nistdigitalarchives.contentdm.oclc.org/digital/api/collection/p16009coll6/id/132609/download ), 70% thermal efficiency, no heat recovery, delivered industrial steam heat in MJ. .02kWh/kg evaporated water for vacuum/mixing/air-condensation is an ENGINEERING allowance, not a measurement; equipment, vacuum pressure and actual duties are unverified. Use generic wastewater treatment for aqueous and steam condensate; do not also emit that condensate directly. Actual contaminants/phase splits and heat integration remain gaps. Retain legacy direct heat-waste allowance without claiming a complete heat-emission balance. Preserve the original implied freight distances but update delivered chemical mass. No other synthesis, battery service, hardware, native inventory, runtime, YAML or indicator change. Sensitivities are reported separately; element/mass closure is not industrial-process certification. </t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Heat, waste</t>
+        </is>
+      </c>
+      <c r="B1230">
+        <v>0.028462</v>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B1231">
+        <v>0.1954582935599618</v>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>TEMPO-4-sulfate potassium production, for RFB</t>
+        </is>
+      </c>
+      <c r="B1232">
+        <v>0.1751844941</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>TEMPO-4-sulfate potassium, electroactive material, RFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>production of 4-HO-TEMPO</t>
+        </is>
+      </c>
+      <c r="B1233">
+        <v>0.11186749303959133</v>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>4-HO-TEMPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>air separation, cryogenic</t>
+        </is>
+      </c>
+      <c r="B1234">
+        <v>0.01357349260833068</v>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>ethyl acetate production</t>
+        </is>
+      </c>
+      <c r="B1235">
+        <v>2.340983906343704</v>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>ethyl acetate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>market for acetone, liquid</t>
+        </is>
+      </c>
+      <c r="B1236">
+        <v>0.6158708214804446</v>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>acetone, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>market for sulfuric acid</t>
+        </is>
+      </c>
+      <c r="B1237">
+        <v>1.383219177935939</v>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>sulfuric acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1238">
+        <v>2.8433120750346514</v>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B1239">
+        <v>0.4738853168674175</v>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1240">
+        <v>0.5035330803161908</v>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1241">
+        <v>0.2171758817332909</v>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>potassium bicarbonate production, from potassium carbonate</t>
+        </is>
+      </c>
+      <c r="B1242">
+        <v>3.251093082716603</v>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>potassium bicarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>steam production, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B1243">
+        <v>10.134874480886907</v>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>treatment of spent solvent mixture, hazardous waste incineration, with energy recovery</t>
+        </is>
+      </c>
+      <c r="B1244">
+        <v>-2.956854727824149</v>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>water production, deionised</t>
+        </is>
+      </c>
+      <c r="B1245">
+        <v>24.66848260112409</v>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>market for heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B1246">
+        <v>90.81039270259532</v>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B1247">
+        <v>195.45829355996182</v>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1248">
+        <v>-0.03531152849669645</v>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1249">
+        <v>-0.013414469031531524</v>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1250">
+        <v>-2.836574920420382</v>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1251">
+        <v>1.2128344554547652</v>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+      <c r="B1252">
+        <v>0.01357349260833068</v>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -7623,7 +7623,9 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+          <t>COMPLETE-SALT MASS FOR ELECTROLYTE CAPACITY, 2026-10-20. Winsberg2017 SI p1, potassium-salt elemental analysis and ESI-MS anion251.08; https://acs.figshare.com/ndownloader/files/7415704. Zhang2025 DOI10.1039/D4EB00027G Table2 declares 40kWh theoretical capacity, 1.25V discharge voltage per cell, and a one-electron TEMPO couple. The inherited 299.797014925373kg dose equals 40000Wh/(1.25V*26.8Ah/mol) *251.08g/mol/1000, using an isolated mass-spectrometry ion mass that omits potassium. The purchased production activity supplies recovered complete salt mass, not a kg of the isolated ion. Use the full C9H17KNO5S formula and average atomic masses: 290.3953g/mol, giving 346.740656716418kg per electrolyte set. Preserve the source 26.8Ah/mol rounding and all other source quantities. Independent Faraday back-calculation gives 34.5864931469411kWh before and 40.0022106633499kWh after; the remaining 0.0056% excess is the documented rounding of 26.80148Ah/mol to 26.8, not a new operational energy gain. Do not add a separate counterion purchase: its manufacture is already inside the supplied salt. This is a pure defined-salt reference; actual recovered-product assay and residual salts/solvent are unreported. Test 90-100% active-salt purity separately rather than certifying a measured commercial composition. Preserve other electrolyte chemicals/water, nominal tank design, hardware, one initial plus22HFB/9OFB replacement sets, round-trip efficiency and delivered-energy denominators. Source nominal whole-battery kg references remain unvalidated adapted-BOM mass proxies; this correction does not claim complete tank hydraulics, density or dry/wet system mass closure. Only this source positive-active-material mass and its explanation change in the existing supplemental workbook; no native/runtime/YAML/method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
         </is>
@@ -7693,7 +7695,7 @@
         <v>487</v>
       </c>
       <c r="B335" s="6">
-        <v>299.79701492537316</v>
+        <v>346.7406567164179</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>7</v>
@@ -7881,7 +7883,9 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
+          <t>COMPLETE-SALT MASS FOR ELECTROLYTE CAPACITY, 2026-10-20. EP3497081A1 Example1 and Janoschka2016 TEMPTMA chloride; https://patents.google.com/patent/EP3497081A1/en. Zhang2025 DOI10.1039/D4EB00027G Table2 declares 40kWh theoretical capacity, 1.0V discharge voltage per cell, and a one-electron TEMPO couple. The inherited 319.701492537313kg dose equals 40000Wh/(1.0V*26.8Ah/mol) *214.2g/mol/1000, using an isolated mass-spectrometry ion mass that omits chloride. The purchased production activity supplies recovered complete salt mass, not a kg of the isolated ion. Use the full C12H26ClN2O formula and average atomic masses: 249.803g/mol, giving 372.840298507463kg per electrolyte set. Preserve the source 26.8Ah/mol rounding and all other source quantities. Independent Faraday back-calculation gives 34.3009232238586kWh before and 40.0022106633499kWh after; the remaining 0.0056% excess is the documented rounding of 26.80148Ah/mol to 26.8, not a new operational energy gain. Do not add a separate counterion purchase: its manufacture is already inside the supplied salt. This is a pure defined-salt reference; actual recovered-product assay and residual salts/solvent are unreported. Test 90-100% active-salt purity separately rather than certifying a measured commercial composition. Preserve other electrolyte chemicals/water, nominal tank design, hardware, one initial plus22HFB/9OFB replacement sets, round-trip efficiency and delivered-energy denominators. Source nominal whole-battery kg references remain unvalidated adapted-BOM mass proxies; this correction does not claim complete tank hydraulics, density or dry/wet system mass closure. Only this source positive-active-material mass and its explanation change in the existing supplemental workbook; no native/runtime/YAML/method edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FLOW-BATTERY FIXED TANK / ELECTROLYTE BOUNDARY, issue78,2026-10-18. Zhang et al.2025 DOI10.1039/D4EB00027G, public paper https://www.db-thueringen.de/servlets/MCRFileNodeServlet/dbt_derivate_00067974/D4EB00027G.pdf . Section2.2 specifies20year tank,stack andperiphery life and chemical electrolyte replacement after degradation. Both original electrolyte recipes also embed124kg HDPE tanks, while the energy subsystem separately buys149kg forHFB or124kg forOFB. Replacing electrolyte22 timesHFB or9timesOFB therefore manufactures tankhardware repeatedly. Remove only the embedded124kg tank exchange from each active electrolyte-unit recipe; keep every chemical,solvent,water quantity and actual batch production amount unchanged. Keep the outer149/124kg installed tank design and its existing HDPE material/extrusion provider once per20year system. Do not replace an entire tank when only electrolyte chemistry is replenished. Preserve the source20year service,40kWh theoretical capacity,round-trip efficiencies,delivered-energy denominators and replacement counts: one initial chemical set plus22HFB or9OFB additional sets. No off-by-one claim about those chemical counts is made. Previously attributed tank manufacture per system:149+124*23=3001kgHFB,124+124*10=1364kgOFB; now149/124kg respectively. This fixes the active duplicate hardware, not an independently validated commercial tank geometry or wall thickness. Published2470kgOFB/2616kgHFB system masses remain nominal source design proxies for legacy kg-market normalization, not certified sums of every adapted component; a complete dry/wet component mass closure depends on inherited periphery and batch yields. Removed duplicated tank quantity must not be reallocated to chemicals or arbitrarymetal. No new end-of-life route for source-excluded organic electrolyte, secondary-share assumption or recovery credit. Other VRFB electrolyte designs and native datasets unchanged. The empty former rows are deliberately removed rather than leaving a zero mean with a nonzero sampled lognormal tank amount.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
         </is>
@@ -7951,7 +7955,7 @@
         <v>489</v>
       </c>
       <c r="B353" s="6">
-        <v>319.70149253731341</v>
+        <v>372.84029850746265</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>7</v>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1252"/>
+  <dimension ref="A1:N1304"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -2749,385 +2749,602 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>466</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>NET HYDROGEN REACTANT CORRECTION, 2026-10-20. https://patents.google.com/patent/CN115010650A/en , Example 1 and process description, carbonyl hydrogenation with excess-H2 recirculation. Source LCA: Zhang et al. 2025, https://doi.org/10.1039/D4EB00027G . Balanced reaction: C9H17NO + H2 -&gt; C9H19NO. One mole of molecular H2 is consumed per mole of ketone, not half a mole. TAA molar mass = 155.241000 g/mol; H2 = 2.016000 g/mol. The existing 0.155241 kg TAA feed therefore requires 0.002016 kg net H2 per declared source batch under the retained full-ketone-conversion reference. This includes conversion of material subsequently lost during isolation: do not apply the isolated-product yield a second time. Use the same RER hydrogen market as the other RFB hydrogenation. In this workbook source-version vocabulary it is named market for hydrogen, liquid; the standard ecoinvent 3.9-to-3.10 migration maps that legacy label to market for hydrogen, gaseous, medium pressure, merchant. This is not an extra hydrogen-liquefaction service. Nitrogen is an inert-gas input and is preserved; air separation cannot supply reacting hydrogen. Recirculation can return EXCESS H2, but cannot return H2 atoms incorporated into product or reaction water. This net stoichiometric amount is an explicit minimum-consumption reference, not measured fresh plant gas. Additional purge/vent losses, side reactions, recycle compression and gross circulating flow are unquantified. No zero-loss industrial claim, new operating-energy allowance or fabricated vent/waste composition is introduced. Preserve existing batch product output, other reagents, utilities, freight, existing waste services, catalyst and battery sizing. The wider process inventory is not certified as mass-balanced by this single-reactant correction. Existing supplemental workbook only; no native inventory, runtime, YAML or indicator-definition changes. The inherited note claimed a 1:0.5 TAA:H2 stoichiometric ratio; that half-equivalent is incorrect for reduction of a ketone to an alcohol. The patent stated circulating 1:1.5 ratio and its example mass flows are not mutually consistent; neither is treated as a measured fresh-gas dose. The selected correction uses the unambiguous one-equivalent chemical requirement. The source Ni/Al2O3 catalyst and its preparation are also missing from this inherited inventory; their dose, nickel fraction and throughput must be reconstructed separately, not silently assumed zero.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-4-OH-TEMP is modeled based on the production process described by "China Pat., CN115010650A, 2022". 15 wt% of triacetone amine in isoprophyl alcohol solvent is mixed with hydrogen in gas-liquid mixer at 110℃, the molar ratio of triacetone amine to hydrogen is 1:1.5. However, since excess hydrogen is recycled and reused for the same process, it is assumed that the molar ratio of triacetone amine to hydrogen rather follows the stoichiometric ratio (1:0.5) per unit of production. The reaction time per unit is assumed to be 3h. The LCI for ethylenediaminetetraacetic acid (EDTA) disodium salt was estimated by the reaction of EDTA with two portions of NaOH in suitable pH.
-The original inventory is presented in: "Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G"</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>468</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.36905150072829601</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>252</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1.9405125000000001E-3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>252</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1.448916E-3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>252</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.15467859</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>4</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.15524099999999999</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>491</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.002016</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>254</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.112549725</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>255</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1.9405125000000001E-3</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>258</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1.4489160000000001</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>257</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2.68790725E-2</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>259</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.10251430575786</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>256</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.16127443499999999</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>260</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="1">
-        <v>-0.112549725</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>261</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -25817,6 +26034,1202 @@
         </is>
       </c>
     </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>production of 4-HO-TEMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>4-HO-TEMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>OMITTED HYDROGENATION CATALYST, 2026-10-20. CN115010650A Example1, https://patents.google.com/patent/CN115010650A/en : 15wt% TAA in liquid feed, 94.56kg/h liquid, WHSV4.73/h, twelve weeks continuous feeding. WHSV refers to the entire liquid, not neat TAA. The implied bed is 94.56/4.73=19.99154334kg; the source loads CALCINED catalyst. Our supplied catalyst reference is REDUCED dry mass. For 20wt% Ni in reduced solids, calcined/reduced mass=1+0.2*15.999/58.6934=1.0545172 (NiO loses O during activation). Treat the WHSV denominator as this loaded calcined mass; divide by that ratio before buying reduced catalyst. This basis interpretation is explicit and the alternative reduced-bed basis is a sensitivity. One bed per demonstrated 2016h campaign therefore gives 0.000662984543206423kg catalyst/kg TAA, or 0.000102922383471908kg for this 0.155241kg TAA/0.15467859kg product batch. This is a campaign-attributed reference; the source does not establish that the bed is exhausted after twelve weeks, actual annual utilization, regeneration or maximum service life. Test 4/12/52week campaigns. New dedicated nickel-on-aluminium-oxide production supplies the omitted catalyst. Its selected 20wt% reduced-metal loading is an analogue assumption, not a measurement for this patent. Do not use the existing methanation catalyst: it purchases metallic AlMg3, not alumina, and its composition/process is not demonstrated equivalent. Add equal negative dry spent-catalyst mass to the RER underground-deposit waste market, an explicit containment proxy; actual spent assay, hazard classification and treatment are unreported. No recycling/substitution credit or invented primary/secondary split. Preserve TAA, ketone-reduction H2, solvents, original utilities, output and battery duty. Catalyst manufacturing/activation H2 is purchased within its own provider once. This correction includes an explicit uncertain manufacturing reference, not certification of an industrial factory or complete organic-battery LCI. Existing supplemental workbook only; no native/runtime/YAML changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>Heat, waste</t>
+        </is>
+      </c>
+      <c r="B1264">
+        <v>0.369051500728296</v>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>air::lower stratosphere + upper troposphere</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+      <c r="B1265">
+        <v>0.0019405125</v>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B1266">
+        <v>0.001448916</v>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>production of 4-HO-TEMP</t>
+        </is>
+      </c>
+      <c r="B1267">
+        <v>0.15467859</v>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>4-HO-TEMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>triacetonamine production</t>
+        </is>
+      </c>
+      <c r="B1268">
+        <v>0.155241</v>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>triacetonamine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>market for hydrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1269">
+        <v>0.002016</v>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>hydrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>market for isopropanol</t>
+        </is>
+      </c>
+      <c r="B1270">
+        <v>0.112549725</v>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>isopropanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1271">
+        <v>0.0019405125</v>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>market for steam, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B1272">
+        <v>1.448916</v>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B1273">
+        <v>0.0268790725</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1274">
+        <v>0.10251430575786</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1275">
+        <v>0.161274435</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>treatment of spent solvent mixture, hazardous waste incineration, with energy recovery</t>
+        </is>
+      </c>
+      <c r="B1276">
+        <v>-0.112549725</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>catalyst production, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+      <c r="B1277">
+        <v>0.00010292238347190828</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>catalyst, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1278">
+        <v>-0.00010292238347190828</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>catalyst production, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>catalyst, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>https://patents.google.com/patent/CN115010650A/en; https://doi.org/10.1007/s10562-021-03884-2; https://www.shepchem.com/chemistry/nickel-nitrate-solution-13/; https://environmentclearance.nic.in/writereaddata/Online/TOR/12_Sep_2017_121716393XNVOK34HAnnexure-Pre-feasibilityReport%28PFR%29File.pdf; https://doi.org/10.3390/molecules25040803; https://www.epa.gov/sites/default/files/2020-09/documents/final_background_document_for_nitric_acid_section_8.8.pdf; https://nepis.epa.gov/Exe/ZyPURL.cgi?Dockey=9100E3DR.TXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>NICKEL-ON-ALUMINA CATALYST PROCESS REFERENCE, 2026-10-20. CN115010650A uses commercial shaped alumina, nickel-nitrate impregnation, drying120C10h and calcination400C3h, but omits loading and manufacture LCI. Select 20wt% Ni in a reduced dry catalyst: the explicit reduced/passivated basis in https://doi.org/10.1007/s10562-021-03884-2 is a loading analogue, not performance evidence for TAA hydrogenation. Use 80wt% non-metallurgical alumina as a support-supply proxy; its exact gamma phase, pore area and shaped carrier process remain unverified. Nickel nitrate manufacturer https://www.shepchem.com/chemistry/nickel-nitrate-solution-13/ confirms dissolution of nickel metal in nitric acid. Integrated chemistry follows the metal/acid reference in Pacific Organics2017 PFRp60 https://environmentclearance.nic.in/writereaddata/Online/TOR/12_Sep_2017_121716393XNVOK34HAnnexure-Pre-feasibilityReport%28PFR%29File.pdf : Ni+4HNO3+4H2O -&gt; Ni(NO3)2.6H2O+2NO2; nitrate calcination produces NiO+2NO2+0.5O2+6H2O; NiO+H2 -&gt; Ni+H2O. Net per Ni: 4HNO3+H2 -&gt; 4NO2+0.5O2+3H2O. Nickel atoms remain in catalyst, not reaction products. The native nitric-acid input is kg PURE HNO3 in 50wt% stock, with one equal kg carrier water; add no duplicate stock water. Fully dry this water plus reaction water to generic air Water in m3 (1000kg/m3). No acid crystallization intermediate is purchased again. Hydrogen activation is supported as an operation by the ketone-hydrogenation preparation analogue https://doi.org/10.3390/molecules25040803; its detailed loading claim conflicts with its gram recipe, so that gram recipe is NOT used as a quantitative BOM. Reference activation uses one net H2/Ni; additional purges and incomplete reduction remain unmeasured. Assumed 95% retention of both solids: buy 1/0.95 gross Ni/alumina, dispose exactly the 0.05263158kg dry loss once without organic-waste combustion. Product contains 0.2kg Ni+0.8kg Al2O3/kg. Thermal50MJ/kg and auxiliary1kWh/kg are explicit engineering allowances for precursor manufacture, impregnation, drying, calcination, shaping activation, scrubbing and residue drying, not measured or derived from holding time alone. Reference water evaporation is about 5.86kg/kg catalyst; thermal duty is not allowed to silently disappear. One Nm3 N2/kg at1.25kg/Nm3 is a purge allowance with equal air release. PFRp61 explicitly sends nitrate-manufacture NO2 to a scrubber, with no measured removal efficiency or reagent budget. Include an explicit 90% caustic-capture reference for both precursor and calcination NO2; this is a selected model, not the factory specification. EPA documents alkaline NOx absorption and nitrate/nitrite waste https://www.epa.gov/sites/default/files/2020-09/documents/final_background_document_for_nitric_acid_section_8.8.pdf and reported 90% examples https://nepis.epa.gov/Exe/ZyPURL.cgi?Dockey=9100E3DR.TXT. 2NO2+2NaOH -&gt; NaNO2+NaNO3+H2O. Purchase one mole pure NaOH per captured mole NO2 via the 50wt% stock; add 8kg DI water/kg pure NaOH to obtain a 10wt% starting solution (stock already carries 1kg/kg). Internal recirculated scrubber water is not purchased repeatedly. Dry the net blowdown water and contain its calculated nitrate/nitrite salts with manufacturing solids in the underground-deposit proxy, not an organic incineration profile or uncharacterized discharge. Actual industrial wastewater treatment, salt oxidation and efficiency remain unverified; containment is not a measured hazard classification. No recovered acid or fertilizer credit. Only the uncaptured NO2 reaches air, expressed as kg NO2 in the native NOx flow. Calculated oxygen release (0.0573865294kg/kg catalyst) is retained in the reaction/mass ledger and this documentation, with no oxygen-product credit. It has zero CF in every selected EF3.1 category and its generic emission flow is absent from the available ecoinvent3.6 biosphere, so no unsupported oxygen biosphere row is inserted. The reaction ledger includes this uncharacterized release; do not claim that summing only the biosphere rows gives complete foreground mass closure. Engineering sensitivities cover loading, retention, campaign life and manufacturing utilities. GLO supply with mixed background geographies is a modelling reference, not the original Chinese plant. Spent catalyst treatment belongs to the consuming reaction; do not dispose the sold 1kg catalyst again in this production provider. No recovery credits, native or runtime changes. Element closure checks bookkeeping only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>catalyst production, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+      <c r="B1291">
+        <v>1</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>catalyst, nickel on aluminium oxide, hydrogenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1292">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B1293">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>market for nitric acid, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B1294">
+        <v>0.9040665022320273</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>nitric acid, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B1295">
+        <v>0.5164693292261141</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1296">
+        <v>4.131754633808913</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>market for hydrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1297">
+        <v>0.007231154655064778</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>hydrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1298">
+        <v>1.25</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>market for heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+      <c r="B1299">
+        <v>50.0</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>heat, from steam, in chemical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1300">
+        <v>1.0</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1301">
+        <v>-1.0468413445141238</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Nitrogen oxides</t>
+        </is>
+      </c>
+      <c r="B1302">
+        <v>0.06600580752108234</v>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B1303">
+        <v>0.005862455348864654</v>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+      <c r="B1304">
+        <v>1.25</v>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1304"/>
+  <dimension ref="A1:N1357"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -21406,1270 +21406,1322 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t/>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B1081">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>source</t>
+          <t/>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 650V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 650V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
-APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
- BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 2.6459999999999997e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 5.601e-06, 'carbon': 2.0046e-05, 'epoxy': 0.00038086799999999997, 'silica': 0.0016036569999999999, 'Sn': 3.2692e-05, 'Ni': 2.9065e-05, 'Sb': 1.26e-07, 'Ag': 3.14e-07}</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>name</t>
+          <t/>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t/>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t/>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t>type</t>
+          <t/>
         </is>
       </c>
       <c r="G1087" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="H1087" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="I1087" t="inlineStr">
         <is>
-          <t>product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
-        </is>
-      </c>
-      <c r="B1088">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t>production</t>
+          <t/>
         </is>
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>silicon carbide wafer production, physical vapour transport</t>
-        </is>
-      </c>
-      <c r="B1089">
-        <v>2.6459999999999997e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t/>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>market for phosphorus, white, liquid</t>
-        </is>
-      </c>
-      <c r="B1090">
-        <v>1.192e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B1091">
-        <v>3.972e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1092">
-        <v>0.003967074</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
       <c r="I1092" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
-        </is>
-      </c>
-      <c r="B1093">
-        <v>5.601e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t/>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B1094">
-        <v>2.0046e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B1095">
-        <v>0.00038086799999999997</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>market for silica sand</t>
-        </is>
-      </c>
-      <c r="B1096">
-        <v>0.0016036569999999999</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>market for tin</t>
-        </is>
-      </c>
-      <c r="B1097">
-        <v>3.2692e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B1098">
-        <v>2.9065e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1098" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
       <c r="I1098" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>market for antimony</t>
-        </is>
-      </c>
-      <c r="B1099">
-        <v>1.26e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1099" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
       <c r="I1099" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>market for silver</t>
-        </is>
-      </c>
-      <c r="B1100">
-        <v>3.14e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
       <c r="I1100" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B1101">
-        <v>0.006047253</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t/>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1101" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
       <c r="I1101" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t/>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B1106">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>source</t>
+          <t/>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-Nomenclature revision, 2026-10-19. Former activity name: RFB AC-stage 1200V SiC switch, TO247 material reference. Former reference product: RFB AC-stage 1200V SiC switch, TO247 material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
-APPROVED FLOW-BATTERY BIDIRECTIONAL CONVERSION REFERENCE, issue109,2026-10-18. Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf . Replace original18kg-labelledsolar-inverter recipe with an explicit two-stage reference,notanassumedpercentagecut inpreciousmetals. DCstage18parallel300Wmoduleequivalents=5.4kW nominal,soeachcarries~21.37Aat13Vand5kWtotal,below300W/12V=25A. HFB13.75V is1.85%abovepublished13.5Vcontrolrange:extendingreferencecontrolsetpointto14V is an EXPLICITengineeringadaptation,NOTTItestedqualification. Selected60V/100VlowFETvoltageclasses leavevoltageheadroom,butflux,loopstability,saturation,sharing,hot-loop layoutandthermalmargins requirehardwareverification. Retain5kWACoutput;ACreferenceisonefull10kWratedbidirectionalTtypeboard,notfractionalphysicalswitches. Grid400V3phase/nominal800VDC TI01606 ACstage requires a matchedDC-link:DCtransformer HV400Vsource is adapted to800V via doubleseriesmoduleHVports while18LVportsparallel;use18moduleequivalentsas9stringswithtwo400Vports perstring,eachLVporthandles~278W and~21.37Aat13V. This series-parallelconnectionandisolation/common-modecontrolis an engineeringarchitecture,notacertifiedmanufacturer system. HVmodulemax400Vperport;2ports800V. No direct13Vbatteryconnectiontoan800Vsolarinput. Currentat5kWAC400V3phase=7.22Arms. Existing RFBroundtrip.70/.73 alreadyincludesconversion:pumps,transformers,inverters;doNOTaddoperatinglossesto1.42857/1.36986kWhcharginginput. Keep40kWhcapacity,chemicalstocks,replacementcounts and20yearperiphery life as selectedsourceassumptions. Source20yearinverterlife remains unvalidated;10-20yearlife sensitivity,not silently doubled.
- BOM-derived DCstagecounts126TO220powerFETs(72HV,54LV),72dualdrivers,18MCUs;AC12SiCswitches+12isolateddrivers+oneMCU. HVTO220usesTI100VTO220CSD19536KCS materialpackageanalogue,NOTvoltage-compatiblepartsubstitutionfor650VIPP60R199CP;LV100Vpart ismaterialanaloguefor60VFDP. HighvoltageSi-diearea/doping/leadattachandpackagemassesneedmanufacturer-specificMCD. DriverUCC27524AQDRQ1 exactfamilyMCD;TMS320F28035PNT64pinMCU asguidepackagechoice;sourceBOMcontrolcardomittedfrompowerboardBOMbutguideexplicitlyrequiresit. AC650/1200VTO247usesexistingInfineonMCDanalogueforTIWolfspeedparts andUCC21710materialanalogueforall12driverpackages. Selectfirstmanufacturerassemblyvariantonly,doNOTsumalternatives. UnknownCSDmetalhydroxide42.368368mg/part isleftUNRESOLVED,notassignedinventedAlorzerometals;tinyMCUproprietaryfractionalso unresolved. Fusedsilica/semiconductorSi/SiCpowder feedproxies lackmeasuredwaferfabrication/yields;1kWh/kgpackageassembly is allowanceonly. Separatefittedboards:18*.025m2 DCpower/controlPCB+0.10m2AC=.55m2,assumed3.08kg/m2. Noextra mountedboard ICproxy on topofMCDs. PerDCmodulemagneticsassume.08kgtransformerCu+.02kginductorCu+.12kgferrite;18setsuse1.8kgCu from ORIGINAL3.06kgCu budget,leaving1.26kgforACfilters,wiring,busbars. .12kg/core andPCBareasareengineeringgeometryassumptions,notrecoveredmanufacturerweights. OriginalAl7.64kg,steel1.45kg,PP1.41kgoutsideelectronics retainedasmechanicalbudget;Cu3.06kgcountedonce andwireprocessingonce. NewsemiconductorandbarePCBmetalsareassumedoutsidebulkmaterialbudget;ownershipuncertaintyexplicit,sensitivityrequired. Keep0.412kgAl-electrolytic and.267kgfilmcapreferencebudgets;18*3*330uF25Vsmallcapsarecontainedwithin.412kg,notaddedagain. Misc0.01kgSMTresistor+.01kgSMTdiode+.01kgconnectorallowsremainingtinyfittedparts,notguaranteedcompleteBOM. Transformerwindingfabrication,gatepulse-transformers,EMC,signal-sensors,communications andcoolingremainqualifiedcoveragegaps. Nominalfinishedmasscomputedfromretainedknownbudgetsplusfullpackagemassesincludingunresolvedfractions;notrenormalizedto18kg. OldLCD/legacylogic/memory/passivecomponentpurchases andtheirPCBwastelineare removedfromactivewrapper. Addmatchedwhole-deviceWEEEonce,newhelpershave noownEOL. Keep2.91kgpaperboard+.0184kgPEpackagingwithmatchingwasteonce;source5.72MJgas+.361MJfuelheat+16.9kWhfactoryelectricity isretainedunit-levelassemblyallowance,notfullnewfactoryqualification. Oldrecipeavailableinbefore-snapshot,notkeptasactiveparallelmanufacture. Existingworkbookonly;no runtime/native/primary-secondaryshare edits. InfineonMCDanaloguehttps://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf andhttps://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf ;ledgerkg={'SiC': 4.941e-06, 'P': 1.192e-06, 'steel': 3.972e-06, 'Cu': 0.003967074, 'Al': 4.257e-06, 'carbon': 2.0032e-05, 'epoxy': 0.000380613, 'silica': 0.00160258, 'Sn': 3.3233e-05, 'Ni': 2.9065e-05, 'Sb': 2.0899999999999998e-07, 'Ag': 5.23e-07}</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>name</t>
+          <t/>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t/>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t/>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t>type</t>
+          <t/>
         </is>
       </c>
       <c r="G1112" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="H1112" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="I1112" t="inlineStr">
         <is>
-          <t>product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
-        </is>
-      </c>
-      <c r="B1113">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t>production</t>
+          <t/>
         </is>
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>silicon carbide wafer production, physical vapour transport</t>
-        </is>
-      </c>
-      <c r="B1114">
-        <v>4.941e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1114" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
       <c r="H1114" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t/>
         </is>
       </c>
       <c r="I1114" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>market for phosphorus, white, liquid</t>
-        </is>
-      </c>
-      <c r="B1115">
-        <v>1.192e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1115" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I1115" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B1116">
-        <v>3.972e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1116" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
       <c r="I1116" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1117">
-        <v>0.003967074</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1117" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
       <c r="I1117" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
-        </is>
-      </c>
-      <c r="B1118">
-        <v>4.257e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t/>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1118" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
       <c r="I1118" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B1119">
-        <v>2.0032e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1119" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
       <c r="I1119" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B1120">
-        <v>0.000380613</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1120" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I1120" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>market for silica sand</t>
-        </is>
-      </c>
-      <c r="B1121">
-        <v>0.00160258</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1121" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
       <c r="I1121" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>market for tin</t>
-        </is>
-      </c>
-      <c r="B1122">
-        <v>3.3233e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1122" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
       <c r="I1122" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B1123">
-        <v>2.9065e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1123" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
       <c r="I1123" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>market for antimony</t>
-        </is>
-      </c>
-      <c r="B1124">
-        <v>2.0899999999999998e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1124" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
       <c r="I1124" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>market for silver</t>
-        </is>
-      </c>
-      <c r="B1125">
-        <v>5.23e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1125" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
       <c r="I1125" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B1126">
-        <v>0.006047690999999999</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t/>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G1126" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
       <c r="I1126" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -27227,6 +27279,1338 @@
       <c r="G1304" t="inlineStr">
         <is>
           <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, redox-flow battery converter, 650 V, TO-247</t>
+        </is>
+      </c>
+      <c r="B1316">
+        <v>1</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1317">
+        <v>4.231554720168967e-06</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1318">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1319">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1320">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1321">
+        <v>5.601e-06</v>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1322">
+        <v>2.0046e-05</v>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1323">
+        <v>0.00038086799999999997</v>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1324">
+        <v>0.0016036569999999999</v>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1325">
+        <v>3.2692e-05</v>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1326">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1327">
+        <v>1.26e-07</v>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1328">
+        <v>3.14e-07</v>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1329">
+        <v>0.12356874832710282</v>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1330">
+        <v>-1.5855547201689676e-06</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Zhang2025 DOI10.1039/D4EB00027G Table2:OFB13cells*1V=13V,HFB11*1.25=13.75V,5kW. TI TIDM-BIDIR-400-12 guideTIDUAI7 and BOMTIDRHT0:300W bidirectional9-13.5V/200-400V,4IPP60R199CP650V+3FDP050AN06A0 60V,4UCC27524A,oneC2000 controller. https://www.ti.com/tool/TIDM-BIDIR-400-12 . AC stage TI TIDA01606 bidirectional10kW architecture and counts already documented inissue97,retainedratedboardat5kW ratherthan5/10partcount. https://www.ti.com/lit/df/tidrvs4g/tidrvs4g.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, redox-flow battery converter, 1200 V, TO-247</t>
+        </is>
+      </c>
+      <c r="B1343">
+        <v>1</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, redox-flow battery converter, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1344">
+        <v>7.901780752968583e-06</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1345">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1346">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1347">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1348">
+        <v>4.257e-06</v>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1349">
+        <v>2.0032e-05</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1350">
+        <v>0.000380613</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1351">
+        <v>0.00160258</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1352">
+        <v>3.3233e-05</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1353">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1354">
+        <v>2.0899999999999998e-07</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1355">
+        <v>5.23e-07</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1356">
+        <v>0.2255010955393859</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1357">
+        <v>-2.960780752968583e-06</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -2723,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1357"/>
+  <dimension ref="A1:N1378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5" style="1" customWidth="1"/>
@@ -5897,233 +5897,365 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>492</v>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>70</v>
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A186" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>7</v>
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A187" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>493</v>
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>10</v>
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>19</v>
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A190" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>472</v>
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A191" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>468</v>
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A192" s="1" t="s">
-        <v>12</v>
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A193" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>8</v>
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A194" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B194" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>252</v>
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G194" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A195" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="B195" s="1">
-        <v>1.363</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H195" s="1" t="s">
-        <v>493</v>
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A196" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B196" s="1">
-        <v>0.72916000000000003</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G196" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>286</v>
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B197" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H197" s="1" t="s">
-        <v>260</v>
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H197" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A198" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B198" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G198" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H198" s="1" t="s">
-        <v>268</v>
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A199" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B199" s="1">
-        <v>0.65380000000000005</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G199" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>285</v>
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -28614,6 +28746,446 @@
         </is>
       </c>
     </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>zinc chloride (ZnCl2) production, electroactive RFBs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>d9b79177394946b58cefbc09b167204d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>zinc chloride (ZnCl2), electroactive RFBs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>DRY ZINC-CHLORIDE MANUFACTURE REFERENCE,2026-10-20. User selected dry salt supply with aqueous supply tested separately. Retain source 0.6538kgZn+0.72916kgPURE-equivalentHCl per1.363kg nominal ZnCl2. Zn+2HCl-&gt;ZnCl2+H2 generates0.02016kgH2 per source batch. The existing0.02kgHydrogen-to-air row already represents this rounded source byproduct; retain it exactly and do not add another H2flow. Exact common-atomic-mass salt is1.3628kg; inherited1.363kg is source rounding (0.0147%),not a large sizing error. Do not silently change metal feeds or the rounded product reference. The30wt% acid supplier carries 1.70137333333333kg water in this batch; its purchase already includes this carrier,so do not buy it again. Dry reference removes it as Water to air,in cubic meters at1000kg/m3. Nominal unrecovered reactionH2 goes to air with no sale,energy or recycling credit; actual gas capture/acid fumes/impurity purification are unknown. UN ECAFE1965 Asian Industrial Development NewsNo1,p97 documents Zn/HCl dissolution,H2,filtration and evaporation/fusion around300C. https://repository.unescap.org/items/f7aa8333-be2e-4a42-97d5-63438c4e11eb/full (indexed process text inspected; fullPDF inaccessible in this session). Commercial solid grades exist,for example98-100.5%assay https://anmolchem.in/Zinc-Chloride-USP.php ; this is availability evidence,not plant-LCI or measured yield. Original study Zhang2025 DOI10.1039/D4EB00027G doesnot specify supplied phase. Selected dry reference requires explicit utilities rather than treating reagent purchases as complete manufacture. Water-only gross load uses25-&gt;100C,cp4.18kJ/kgK andlatent2255kJ/kg (NIST https://www.nist.gov/document/chapter-9pdf),giving 4.36997740666667MJ/batch. Add an EXPLICIT1MJ/kg salt finishing/dehydration allowance,not measured ZnCl2heat capacity or fusion enthalpy. Divide useful process load by selected0.70equipment heat-transfer utilization. Native furnace already models fuel conversion; do not add/divide by a second combustion efficiency. This gives 8.18996772380952MJ purchased industrial-gas furnace heat per source batch. It is an engineering reference,not measured commercial energy. Dissolution exotherm is assumed unrecovered in a cooled initial operation; test recovered heat separately,without a fictitious energy coproduct. No recovered condensate credit. Auxiliary0.10kWh/kg salt covers assumed agitation,pumping,filtration and controls; it is not a measured equipment BOM. Test finishing0.3-3MJ/kg,transfer0.4-0.9,aux0.02-0.3 kWh/kg and50%water-heat recovery coherently. Actual boiling elevation/vacuum,hydration/purity,plant losses,utilities/emissions and gas management remain unqualified. No invented trace-metal assay or primary/secondary split. Source Zn/acid/transport/output, HFB salt doses and downstream water,capacity,hardware,chemical replacements and lifetime denominators are unchanged. Aqueous counterfactual must retain carrier in product,subtract it from make-up water and scale delivery transport; do not apply dry evaporation to that counterfactual. Existing supplemental workbook only; no runtime,YAML or method changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Zhang, S., Ramanujam, A. S., Arvidsson, R., Michieletto, A., &amp; Schubert, U. S. (2025). Prospective life cycle assessment of organic redox flow batteries. EES Batteries. doi: https://doi.org/10.1039/D4EB00027G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B1370">
+        <v>0.02</v>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>zinc chloride (ZnCl2) production, electroactive RFBs</t>
+        </is>
+      </c>
+      <c r="B1371">
+        <v>1.363</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>vanadium-organic-and-hybrid-redox-flow-battery</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>zinc chloride (ZnCl2), electroactive RFBs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="B1372">
+        <v>0.72916</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>market for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1373">
+        <v>0.6</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+      <c r="B1374">
+        <v>0.1</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry 16-32 metric ton, EURO5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1375">
+        <v>0.6538</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>cutoff39</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>heat production, natural gas, at industrial furnace &gt;100kW</t>
+        </is>
+      </c>
+      <c r="B1376">
+        <v>8.189967723809524</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1377">
+        <v>0.1363</v>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B1378">
+        <v>0.0017013733333333333</v>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>biosphere3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R933" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-organic-and-hybrid-redox-flow.xlsx
@@ -17865,8 +17865,12 @@
       <c r="A911" t="s">
         <v>43</v>
       </c>
-      <c r="B911" t="s">
-        <v>570</v>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>CURRENT-BOM KILOGRAM NORMALIZATION,2026-10-20. This market supplies one nominal kilogram of the current installed battery assembly. The former1/2470.0 assembly fraction used the Zhang2025 Table2 published design mass before adapted stack,pure-salt and converter inventories. It now bought 1.02743076888572 modeledkg for a1kg reference. Sum current FINISHED installed components,not gross manufacturing feeds,metalworking services,packaging,waste or lifetime replacement electrolytes: electrolyte2262.2671641791kg + stack112.027575603796kg + fixedtanks124kg + periphery39.45925936483kg = 2537.75399914773kg. Periphery includes 0.624kgcable+0.344kgpipe+the existing18.49125936483kg converter nominal finished-mass ledger+two10kg nominal pumps. Pump10kg is the EXISTING documented40W-provider mass-scaling assumption, not newly measured500W or manufacturer-specific mass. The updated converter mass matches its existing whole-device treatment amount. Each stack purchase iskgfinishedcomponent and is counted once; do not unfold raw-feed yields and count the same material twice. Electrolyte sum is the current defined-salt plus nominal solvent reference,not measured mixture density/assay. A future aqueous ZnCl2 alternative must subtract carried water frommakeup to retain the same total solvent reference; current approved dry supply removes that carrier before delivery. Buy1/2537.75399914773 assemblyunits/kg; current theoretical capacity is0.0157619690535148kWh/kg. Preserve the entire40kWh cell/subsystem recipes and lifetime electricity endpoints exactly. This corrects the kg reference contract of the selected engineering BOM; it does not certify real equipment mass,chemical assay,hydraulics,pump/converter performance or commercial energy density. Retain all such evidence gaps. Only this market coefficient and its documentation change. No native/runtime,YAML,method,learning-curve,hardware/duty or primary/secondary-share changes. Source design: https://doi.org/10.1039/D4EB00027G .
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Effective energy density: 16 W h/kg. Net capacity:</t>
+        </is>
       </c>
       <c r="C911"/>
       <c r="D911"/>
@@ -18013,8 +18017,8 @@
         <v>504</v>
       </c>
       <c r="B920" s="4">
-        <f>1/2470</f>
-        <v>4.0485829959514168E-4</v>
+        <f>1/2537.75399914773</f>
+        <v>0.00039404922633787053</v>
       </c>
       <c r="C920" s="1" t="s">
         <v>7</v>
@@ -18028,8 +18032,10 @@
       <c r="G920" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="H920" s="1" t="s">
-        <v>572</v>
+      <c r="H920" s="1" t="inlineStr">
+        <is>
+          <t>CURRENT-BOM KILOGRAM NORMALIZATION,2026-10-20. This market supplies one nominal kilogram of the current installed battery assembly. The former1/2470.0 assembly fraction used the Zhang2025 Table2 published design mass before adapted stack,pure-salt and converter inventories. It now bought 1.02743076888572 modeledkg for a1kg reference. Sum current FINISHED installed components,not gross manufacturing feeds,metalworking services,packaging,waste or lifetime replacement electrolytes: electrolyte2262.2671641791kg + stack112.027575603796kg + fixedtanks124kg + periphery39.45925936483kg = 2537.75399914773kg. Periphery includes 0.624kgcable+0.344kgpipe+the existing18.49125936483kg converter nominal finished-mass ledger+two10kg nominal pumps. Pump10kg is the EXISTING documented40W-provider mass-scaling assumption, not newly measured500W or manufacturer-specific mass. The updated converter mass matches its existing whole-device treatment amount. Each stack purchase iskgfinishedcomponent and is counted once; do not unfold raw-feed yields and count the same material twice. Electrolyte sum is the current defined-salt plus nominal solvent reference,not measured mixture density/assay. A future aqueous ZnCl2 alternative must subtract carried water frommakeup to retain the same total solvent reference; current approved dry supply removes that carrier before delivery. Buy1/2537.75399914773 assemblyunits/kg; current theoretical capacity is0.0157619690535148kWh/kg. Preserve the entire40kWh cell/subsystem recipes and lifetime electricity endpoints exactly. This corrects the kg reference contract of the selected engineering BOM; it does not certify real equipment mass,chemical assay,hydraulics,pump/converter performance or commercial energy density. Retain all such evidence gaps. Only this market coefficient and its documentation change. No native/runtime,YAML,method,learning-curve,hardware/duty or primary/secondary-share changes. Source design: https://doi.org/10.1039/D4EB00027G .</t>
+        </is>
       </c>
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.2">
@@ -18074,8 +18080,12 @@
       <c r="A924" t="s">
         <v>43</v>
       </c>
-      <c r="B924" t="s">
-        <v>571</v>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>CURRENT-BOM KILOGRAM NORMALIZATION,2026-10-20. This market supplies one nominal kilogram of the current installed battery assembly. The former1/2616.0 assembly fraction used the Zhang2025 Table2 published design mass before adapted stack,pure-salt and converter inventories. It now bought 1.0329177200514 modeledkg for a1kg reference. Sum current FINISHED installed components,not gross manufacturing feeds,metalworking services,packaging,waste or lifetime replacement electrolytes: electrolyte2325.97946268657kg + stack187.674033603076kg + fixedtanks149kg + periphery39.45925936483kg = 2702.11275565447kg. Periphery includes 0.624kgcable+0.344kgpipe+the existing18.49125936483kg converter nominal finished-mass ledger+two10kg nominal pumps. Pump10kg is the EXISTING documented40W-provider mass-scaling assumption, not newly measured500W or manufacturer-specific mass. The updated converter mass matches its existing whole-device treatment amount. Each stack purchase iskgfinishedcomponent and is counted once; do not unfold raw-feed yields and count the same material twice. Electrolyte sum is the current defined-salt plus nominal solvent reference,not measured mixture density/assay. A future aqueous ZnCl2 alternative must subtract carried water frommakeup to retain the same total solvent reference; current approved dry supply removes that carrier before delivery. Buy1/2702.11275565447 assemblyunits/kg; current theoretical capacity is0.0148032312553558kWh/kg. Preserve the entire40kWh cell/subsystem recipes and lifetime electricity endpoints exactly. This corrects the kg reference contract of the selected engineering BOM; it does not certify real equipment mass,chemical assay,hydraulics,pump/converter performance or commercial energy density. Retain all such evidence gaps. Only this market coefficient and its documentation change. No native/runtime,YAML,method,learning-curve,hardware/duty or primary/secondary-share changes. Source design: https://doi.org/10.1039/D4EB00027G .
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Effective energy density: 15 W h/kg. Net capacity:</t>
+        </is>
       </c>
       <c r="C924"/>
       <c r="D924"/>
@@ -18222,8 +18232,8 @@
         <v>502</v>
       </c>
       <c r="B933" s="4">
-        <f>1/2616</f>
-        <v>3.8226299694189603E-4</v>
+        <f>1/2702.112755654473</f>
+        <v>0.00037008078138389607</v>
       </c>
       <c r="C933" s="1" t="s">
         <v>7</v>
@@ -18237,8 +18247,10 @@
       <c r="G933" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="H933" s="1" t="s">
-        <v>572</v>
+      <c r="H933" s="1" t="inlineStr">
+        <is>
+          <t>CURRENT-BOM KILOGRAM NORMALIZATION,2026-10-20. This market supplies one nominal kilogram of the current installed battery assembly. The former1/2616.0 assembly fraction used the Zhang2025 Table2 published design mass before adapted stack,pure-salt and converter inventories. It now bought 1.0329177200514 modeledkg for a1kg reference. Sum current FINISHED installed components,not gross manufacturing feeds,metalworking services,packaging,waste or lifetime replacement electrolytes: electrolyte2325.97946268657kg + stack187.674033603076kg + fixedtanks149kg + periphery39.45925936483kg = 2702.11275565447kg. Periphery includes 0.624kgcable+0.344kgpipe+the existing18.49125936483kg converter nominal finished-mass ledger+two10kg nominal pumps. Pump10kg is the EXISTING documented40W-provider mass-scaling assumption, not newly measured500W or manufacturer-specific mass. The updated converter mass matches its existing whole-device treatment amount. Each stack purchase iskgfinishedcomponent and is counted once; do not unfold raw-feed yields and count the same material twice. Electrolyte sum is the current defined-salt plus nominal solvent reference,not measured mixture density/assay. A future aqueous ZnCl2 alternative must subtract carried water frommakeup to retain the same total solvent reference; current approved dry supply removes that carrier before delivery. Buy1/2702.11275565447 assemblyunits/kg; current theoretical capacity is0.0148032312553558kWh/kg. Preserve the entire40kWh cell/subsystem recipes and lifetime electricity endpoints exactly. This corrects the kg reference contract of the selected engineering BOM; it does not certify real equipment mass,chemical assay,hydraulics,pump/converter performance or commercial energy density. Retain all such evidence gaps. Only this market coefficient and its documentation change. No native/runtime,YAML,method,learning-curve,hardware/duty or primary/secondary-share changes. Source design: https://doi.org/10.1039/D4EB00027G .</t>
+        </is>
       </c>
     </row>
     <row r="936">
